--- a/task132/target/veldtek_rma_log_vpr340_psu.xlsx
+++ b/task132/target/veldtek_rma_log_vpr340_psu.xlsx
@@ -1,1100 +1,1246 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B203ECE7-FA9F-40FD-A705-4377386E392F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{098964F6-30A2-48F1-AFE9-BDD8D800554B}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RMA register" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="RMA register" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'RMA register'!$A$1:$H$129</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="686" uniqueCount="353">
-  <si>
-    <t>rma_no</t>
-  </si>
-  <si>
-    <t>part_no</t>
-  </si>
-  <si>
-    <t>serial_no</t>
-  </si>
-  <si>
-    <t>customer</t>
-  </si>
-  <si>
-    <t>customer_ref</t>
-  </si>
-  <si>
-    <t>received</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>returned</t>
-  </si>
-  <si>
-    <t>RMA-24201</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="398">
+  <si>
+    <t>RMA No.</t>
+  </si>
+  <si>
+    <t>Part No.</t>
+  </si>
+  <si>
+    <t>Serial No.</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>Customer Ref.</t>
+  </si>
+  <si>
+    <t>Date Received</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Date Returned</t>
+  </si>
+  <si>
+    <t>RMA-24207</t>
   </si>
   <si>
     <t>VPR340-PSU-02</t>
   </si>
   <si>
-    <t>PS02-00-21653</t>
-  </si>
-  <si>
-    <t>Ironwood Hydro Distribution</t>
-  </si>
-  <si>
-    <t>WO2104448</t>
+    <t>PS02-02-22525</t>
+  </si>
+  <si>
+    <t>Tarrock Hydro Distribution</t>
+  </si>
+  <si>
+    <t>WO2104964</t>
   </si>
   <si>
     <t>REPAIRED</t>
   </si>
   <si>
-    <t>RMA-24210</t>
-  </si>
-  <si>
-    <t>PS02-03-22374</t>
-  </si>
-  <si>
-    <t>WO2104985</t>
-  </si>
-  <si>
-    <t>RMA-24245</t>
-  </si>
-  <si>
-    <t>PS02-08-23920</t>
-  </si>
-  <si>
-    <t>WO2105862</t>
+    <t>RMA-24214</t>
+  </si>
+  <si>
+    <t>PS02-08-24098</t>
+  </si>
+  <si>
+    <t>WO2106243</t>
   </si>
   <si>
     <t>RMA-24252</t>
   </si>
   <si>
-    <t>PS02-02-22294</t>
-  </si>
-  <si>
-    <t>WO2109739</t>
-  </si>
-  <si>
-    <t>RMA-24288</t>
-  </si>
-  <si>
-    <t>PS02-08-23717</t>
-  </si>
-  <si>
-    <t>WO2112858</t>
+    <t>PS02-02-22441</t>
+  </si>
+  <si>
+    <t>WO2107990</t>
+  </si>
+  <si>
+    <t>RMA-24264</t>
+  </si>
+  <si>
+    <t>PS02-10-25091</t>
+  </si>
+  <si>
+    <t>WO2108496</t>
+  </si>
+  <si>
+    <t>RMA-24300</t>
+  </si>
+  <si>
+    <t>PS02-02-22478</t>
+  </si>
+  <si>
+    <t>WO2109792</t>
   </si>
   <si>
     <t>BEYOND ECONOMIC REPAIR</t>
   </si>
   <si>
-    <t>RMA-24298</t>
-  </si>
-  <si>
-    <t>PS02-07-23174</t>
-  </si>
-  <si>
-    <t>WO2114414</t>
-  </si>
-  <si>
-    <t>RMA-24327</t>
-  </si>
-  <si>
-    <t>PS02-02-22106</t>
-  </si>
-  <si>
-    <t>WO2116048</t>
-  </si>
-  <si>
-    <t>RMA-24344</t>
-  </si>
-  <si>
-    <t>PS02-03-22421</t>
-  </si>
-  <si>
-    <t>WO2117265</t>
-  </si>
-  <si>
-    <t>RMA-24359</t>
-  </si>
-  <si>
-    <t>PS02-01-21987</t>
-  </si>
-  <si>
-    <t>WO2117517</t>
-  </si>
-  <si>
-    <t>RMA-24370</t>
-  </si>
-  <si>
-    <t>PS02-10-24523</t>
-  </si>
-  <si>
-    <t>WO2119440</t>
-  </si>
-  <si>
-    <t>RMA-24409</t>
-  </si>
-  <si>
-    <t>PS02-03-22363</t>
-  </si>
-  <si>
-    <t>WO2120588</t>
-  </si>
-  <si>
-    <t>RMA-24444</t>
-  </si>
-  <si>
-    <t>PS02-05-22768</t>
-  </si>
-  <si>
-    <t>WO2121172</t>
-  </si>
-  <si>
-    <t>RMA-24461</t>
-  </si>
-  <si>
-    <t>PS02-08-23769</t>
-  </si>
-  <si>
-    <t>WO2121138</t>
-  </si>
-  <si>
-    <t>RMA-24470</t>
-  </si>
-  <si>
-    <t>PS02-03-22393</t>
-  </si>
-  <si>
-    <t>WO2121635</t>
-  </si>
-  <si>
-    <t>RMA-24498</t>
-  </si>
-  <si>
-    <t>PS02-05-22867</t>
-  </si>
-  <si>
-    <t>WO2122175</t>
-  </si>
-  <si>
-    <t>RMA-24510</t>
-  </si>
-  <si>
-    <t>PS02-04-22655</t>
-  </si>
-  <si>
-    <t>WO2122357</t>
-  </si>
-  <si>
-    <t>RMA-24547</t>
-  </si>
-  <si>
-    <t>PS02-99-21576</t>
-  </si>
-  <si>
-    <t>WO2122465</t>
+    <t>RMA-24323</t>
+  </si>
+  <si>
+    <t>PS02-99-21828</t>
+  </si>
+  <si>
+    <t>WO2111611</t>
+  </si>
+  <si>
+    <t>RMA-24334</t>
+  </si>
+  <si>
+    <t>PS02-05-23084</t>
+  </si>
+  <si>
+    <t>WO2111672</t>
+  </si>
+  <si>
+    <t>RMA-24346</t>
+  </si>
+  <si>
+    <t>PS02-99-21704</t>
+  </si>
+  <si>
+    <t>WO2112207</t>
+  </si>
+  <si>
+    <t>RMA-24360</t>
+  </si>
+  <si>
+    <t>PS02-06-23232</t>
+  </si>
+  <si>
+    <t>WO2112535</t>
+  </si>
+  <si>
+    <t>RMA-24398</t>
+  </si>
+  <si>
+    <t>PS02-01-22144</t>
+  </si>
+  <si>
+    <t>WO2112883</t>
+  </si>
+  <si>
+    <t>RMA-24416</t>
+  </si>
+  <si>
+    <t>PS02-07-23423</t>
+  </si>
+  <si>
+    <t>WO2113326</t>
+  </si>
+  <si>
+    <t>RMA-24450</t>
+  </si>
+  <si>
+    <t>PS02-01-22191</t>
+  </si>
+  <si>
+    <t>WO2115860</t>
+  </si>
+  <si>
+    <t>RMA-24489</t>
+  </si>
+  <si>
+    <t>PS02-07-23841</t>
+  </si>
+  <si>
+    <t>WO2116951</t>
+  </si>
+  <si>
+    <t>RMA-24504</t>
+  </si>
+  <si>
+    <t>PS02-02-22508</t>
+  </si>
+  <si>
+    <t>WO2117151</t>
+  </si>
+  <si>
+    <t>RMA-24515</t>
+  </si>
+  <si>
+    <t>PS02-00-22023</t>
+  </si>
+  <si>
+    <t>WO2117329</t>
+  </si>
+  <si>
+    <t>RMA-24540</t>
+  </si>
+  <si>
+    <t>PS02-02-22494</t>
+  </si>
+  <si>
+    <t>WO2120699</t>
+  </si>
+  <si>
+    <t>RMA-24577</t>
+  </si>
+  <si>
+    <t>PS02-08-24267</t>
+  </si>
+  <si>
+    <t>WO2120818</t>
   </si>
   <si>
     <t>NO FAULT FOUND</t>
   </si>
   <si>
-    <t>RMA-24587</t>
-  </si>
-  <si>
-    <t>PS02-01-22057</t>
-  </si>
-  <si>
-    <t>WO2124235</t>
-  </si>
-  <si>
-    <t>RMA-24612</t>
-  </si>
-  <si>
-    <t>PS02-04-22589</t>
-  </si>
-  <si>
-    <t>WO2126828</t>
+    <t>RMA-24606</t>
+  </si>
+  <si>
+    <t>PS02-04-22880</t>
+  </si>
+  <si>
+    <t>WO2121123</t>
   </si>
   <si>
     <t>RMA-24635</t>
   </si>
   <si>
-    <t>PS02-02-22208</t>
-  </si>
-  <si>
-    <t>WO2126838</t>
-  </si>
-  <si>
-    <t>RMA-24652</t>
-  </si>
-  <si>
-    <t>PS02-06-23019</t>
-  </si>
-  <si>
-    <t>WO2130020</t>
-  </si>
-  <si>
-    <t>RMA-24679</t>
-  </si>
-  <si>
-    <t>PS02-05-22921</t>
-  </si>
-  <si>
-    <t>WO2130895</t>
-  </si>
-  <si>
-    <t>RMA-24691</t>
-  </si>
-  <si>
-    <t>PS02-04-22628</t>
-  </si>
-  <si>
-    <t>WO2131733</t>
-  </si>
-  <si>
-    <t>RMA-24726</t>
-  </si>
-  <si>
-    <t>PS02-02-22326</t>
-  </si>
-  <si>
-    <t>WO2131991</t>
-  </si>
-  <si>
-    <t>RMA-24760</t>
-  </si>
-  <si>
-    <t>PS02-08-23919</t>
-  </si>
-  <si>
-    <t>WO2132400</t>
+    <t>PS02-02-22503</t>
+  </si>
+  <si>
+    <t>WO2122394</t>
+  </si>
+  <si>
+    <t>RMA-24650</t>
+  </si>
+  <si>
+    <t>PS02-04-22897</t>
+  </si>
+  <si>
+    <t>WO2122474</t>
+  </si>
+  <si>
+    <t>RMA-24673</t>
+  </si>
+  <si>
+    <t>PS02-04-22827</t>
+  </si>
+  <si>
+    <t>WO2122588</t>
+  </si>
+  <si>
+    <t>RMA-24703</t>
+  </si>
+  <si>
+    <t>PS02-06-23382</t>
+  </si>
+  <si>
+    <t>WO2125728</t>
+  </si>
+  <si>
+    <t>RMA-24727</t>
+  </si>
+  <si>
+    <t>PS02-04-22773</t>
+  </si>
+  <si>
+    <t>WO2127693</t>
+  </si>
+  <si>
+    <t>RMA-24739</t>
+  </si>
+  <si>
+    <t>PS02-99-21811</t>
+  </si>
+  <si>
+    <t>WO2128496</t>
+  </si>
+  <si>
+    <t>RMA-24767</t>
+  </si>
+  <si>
+    <t>PS02-12-25778</t>
+  </si>
+  <si>
+    <t>WO2128824</t>
   </si>
   <si>
     <t>RMA-24800</t>
   </si>
   <si>
-    <t>PS02-09-24160</t>
-  </si>
-  <si>
-    <t>WO2133198</t>
-  </si>
-  <si>
-    <t>RMA-24808</t>
-  </si>
-  <si>
-    <t>PS02-02-22176</t>
-  </si>
-  <si>
-    <t>WO2133124</t>
-  </si>
-  <si>
-    <t>RMA-24815</t>
-  </si>
-  <si>
-    <t>PS02-10-24746</t>
-  </si>
-  <si>
-    <t>WO2137386</t>
-  </si>
-  <si>
-    <t>RMA-24829</t>
-  </si>
-  <si>
-    <t>PS02-99-21624</t>
-  </si>
-  <si>
-    <t>WO2138428</t>
-  </si>
-  <si>
-    <t>RMA-24855</t>
-  </si>
-  <si>
-    <t>PS02-09-24126</t>
-  </si>
-  <si>
-    <t>WO2138741</t>
-  </si>
-  <si>
-    <t>RMA-24861</t>
-  </si>
-  <si>
-    <t>PS02-10-24497</t>
-  </si>
-  <si>
-    <t>WO2139995</t>
-  </si>
-  <si>
-    <t>RMA-24878</t>
-  </si>
-  <si>
-    <t>PS02-04-22681</t>
-  </si>
-  <si>
-    <t>WO2140703</t>
-  </si>
-  <si>
-    <t>RMA-24906</t>
-  </si>
-  <si>
-    <t>PS02-04-22705</t>
-  </si>
-  <si>
-    <t>WO2141196</t>
-  </si>
-  <si>
-    <t>RMA-24939</t>
-  </si>
-  <si>
-    <t>PS02-02-22195</t>
-  </si>
-  <si>
-    <t>WO2142116</t>
-  </si>
-  <si>
-    <t>RMA-24971</t>
-  </si>
-  <si>
-    <t>PS02-02-22210</t>
-  </si>
-  <si>
-    <t>WO2145554</t>
-  </si>
-  <si>
-    <t>RMA-25011</t>
-  </si>
-  <si>
-    <t>PS02-01-21995</t>
-  </si>
-  <si>
-    <t>WO2145938</t>
-  </si>
-  <si>
-    <t>RMA-25048</t>
-  </si>
-  <si>
-    <t>PS02-00-21937</t>
-  </si>
-  <si>
-    <t>WO2146180</t>
-  </si>
-  <si>
-    <t>RMA-25069</t>
-  </si>
-  <si>
-    <t>PS02-09-24291</t>
-  </si>
-  <si>
-    <t>WO2146590</t>
+    <t>PS02-99-21768</t>
+  </si>
+  <si>
+    <t>WO2130770</t>
+  </si>
+  <si>
+    <t>RMA-24810</t>
+  </si>
+  <si>
+    <t>PS02-05-23118</t>
+  </si>
+  <si>
+    <t>WO2131268</t>
+  </si>
+  <si>
+    <t>RMA-24820</t>
+  </si>
+  <si>
+    <t>PS02-05-23011</t>
+  </si>
+  <si>
+    <t>WO2131769</t>
+  </si>
+  <si>
+    <t>RMA-24838</t>
+  </si>
+  <si>
+    <t>PS02-08-24092</t>
+  </si>
+  <si>
+    <t>WO2132590</t>
+  </si>
+  <si>
+    <t>RMA-24873</t>
+  </si>
+  <si>
+    <t>PS02-04-22790</t>
+  </si>
+  <si>
+    <t>WO2132796</t>
+  </si>
+  <si>
+    <t>RMA-24887</t>
+  </si>
+  <si>
+    <t>PS02-02-22383</t>
+  </si>
+  <si>
+    <t>WO2132996</t>
+  </si>
+  <si>
+    <t>RMA-24912</t>
+  </si>
+  <si>
+    <t>PS02-99-21771</t>
+  </si>
+  <si>
+    <t>WO2133451</t>
+  </si>
+  <si>
+    <t>RMA-24925</t>
+  </si>
+  <si>
+    <t>PS02-01-22203</t>
+  </si>
+  <si>
+    <t>WO2134486</t>
+  </si>
+  <si>
+    <t>RMA-24949</t>
+  </si>
+  <si>
+    <t>PS02-11-25536</t>
+  </si>
+  <si>
+    <t>WO2137993</t>
+  </si>
+  <si>
+    <t>RMA-24967</t>
+  </si>
+  <si>
+    <t>PS02-99-21682</t>
+  </si>
+  <si>
+    <t>WO2139215</t>
+  </si>
+  <si>
+    <t>RMA-25007</t>
+  </si>
+  <si>
+    <t>PS02-08-24199</t>
+  </si>
+  <si>
+    <t>WO2139976</t>
+  </si>
+  <si>
+    <t>RMA-25037</t>
+  </si>
+  <si>
+    <t>PS02-09-24740</t>
+  </si>
+  <si>
+    <t>WO2140632</t>
+  </si>
+  <si>
+    <t>RMA-25051</t>
+  </si>
+  <si>
+    <t>PS02-04-22838</t>
+  </si>
+  <si>
+    <t>WO2142177</t>
+  </si>
+  <si>
+    <t>RMA-25076</t>
+  </si>
+  <si>
+    <t>PS02-10-24979</t>
+  </si>
+  <si>
+    <t>WO2142255</t>
+  </si>
+  <si>
+    <t>RMA-25082</t>
+  </si>
+  <si>
+    <t>PS02-09-24475</t>
+  </si>
+  <si>
+    <t>WO2142870</t>
   </si>
   <si>
     <t>RMA-25109</t>
   </si>
   <si>
-    <t>PS02-01-22016</t>
-  </si>
-  <si>
-    <t>WO2146690</t>
-  </si>
-  <si>
-    <t>RMA-25135</t>
-  </si>
-  <si>
-    <t>PS02-04-22503</t>
-  </si>
-  <si>
-    <t>WO2147892</t>
-  </si>
-  <si>
-    <t>RMA-25160</t>
-  </si>
-  <si>
-    <t>PS02-00-21951</t>
-  </si>
-  <si>
-    <t>WO2148811</t>
-  </si>
-  <si>
-    <t>RMA-25187</t>
-  </si>
-  <si>
-    <t>PS02-04-22671</t>
-  </si>
-  <si>
-    <t>WO2149274</t>
-  </si>
-  <si>
-    <t>RMA-25221</t>
-  </si>
-  <si>
-    <t>PS02-07-23517</t>
-  </si>
-  <si>
-    <t>WO2151158</t>
-  </si>
-  <si>
-    <t>RMA-25233</t>
-  </si>
-  <si>
-    <t>PS02-04-22517</t>
-  </si>
-  <si>
-    <t>WO2152061</t>
-  </si>
-  <si>
-    <t>RMA-25245</t>
-  </si>
-  <si>
-    <t>PS02-02-22270</t>
-  </si>
-  <si>
-    <t>WO2152770</t>
-  </si>
-  <si>
-    <t>RMA-25253</t>
-  </si>
-  <si>
-    <t>PS02-00-21752</t>
-  </si>
-  <si>
-    <t>WO2153643</t>
-  </si>
-  <si>
-    <t>RMA-25268</t>
-  </si>
-  <si>
-    <t>PS02-00-21765</t>
-  </si>
-  <si>
-    <t>WO2154374</t>
-  </si>
-  <si>
-    <t>RMA-25280</t>
-  </si>
-  <si>
-    <t>PS02-10-24757</t>
-  </si>
-  <si>
-    <t>WO2154554</t>
-  </si>
-  <si>
-    <t>RMA-25289</t>
-  </si>
-  <si>
-    <t>PS02-00-21849</t>
-  </si>
-  <si>
-    <t>WO2158148</t>
-  </si>
-  <si>
-    <t>RMA-25327</t>
-  </si>
-  <si>
-    <t>PS02-10-24571</t>
-  </si>
-  <si>
-    <t>WO2158872</t>
-  </si>
-  <si>
-    <t>RMA-25353</t>
-  </si>
-  <si>
-    <t>PS02-02-22214</t>
-  </si>
-  <si>
-    <t>WO2159033</t>
-  </si>
-  <si>
-    <t>RMA-25370</t>
-  </si>
-  <si>
-    <t>PS02-07-23213</t>
-  </si>
-  <si>
-    <t>WO2159137</t>
-  </si>
-  <si>
-    <t>RMA-25376</t>
-  </si>
-  <si>
-    <t>PS02-07-23463</t>
-  </si>
-  <si>
-    <t>WO2159150</t>
-  </si>
-  <si>
-    <t>RMA-25413</t>
-  </si>
-  <si>
-    <t>PS02-99-21618</t>
-  </si>
-  <si>
-    <t>WO2159757</t>
-  </si>
-  <si>
-    <t>RMA-25440</t>
-  </si>
-  <si>
-    <t>PS02-02-22251</t>
-  </si>
-  <si>
-    <t>WO2159844</t>
-  </si>
-  <si>
-    <t>RMA-25477</t>
-  </si>
-  <si>
-    <t>PS02-05-22870</t>
-  </si>
-  <si>
-    <t>WO2163297</t>
-  </si>
-  <si>
-    <t>RMA-25489</t>
-  </si>
-  <si>
-    <t>PS02-01-22002</t>
-  </si>
-  <si>
-    <t>WO2164441</t>
-  </si>
-  <si>
-    <t>RMA-25506</t>
-  </si>
-  <si>
-    <t>PS02-09-24102</t>
-  </si>
-  <si>
-    <t>WO2164487</t>
-  </si>
-  <si>
-    <t>RMA-25527</t>
-  </si>
-  <si>
-    <t>PS02-09-24372</t>
-  </si>
-  <si>
-    <t>WO2164681</t>
-  </si>
-  <si>
-    <t>RMA-25567</t>
-  </si>
-  <si>
-    <t>PS02-06-23130</t>
-  </si>
-  <si>
-    <t>WO2164804</t>
-  </si>
-  <si>
-    <t>RMA-25574</t>
-  </si>
-  <si>
-    <t>PS02-08-23723</t>
-  </si>
-  <si>
-    <t>WO2165437</t>
-  </si>
-  <si>
-    <t>RMA-25607</t>
-  </si>
-  <si>
-    <t>PS02-11-25178</t>
-  </si>
-  <si>
-    <t>WO2166822</t>
-  </si>
-  <si>
-    <t>RMA-25628</t>
-  </si>
-  <si>
-    <t>PS02-09-24428</t>
-  </si>
-  <si>
-    <t>WO2167031</t>
+    <t>PS02-14-26275</t>
+  </si>
+  <si>
+    <t>WO2142874</t>
+  </si>
+  <si>
+    <t>RMA-25126</t>
+  </si>
+  <si>
+    <t>PS02-01-22136</t>
+  </si>
+  <si>
+    <t>WO2145207</t>
+  </si>
+  <si>
+    <t>RMA-25164</t>
+  </si>
+  <si>
+    <t>PS02-06-23389</t>
+  </si>
+  <si>
+    <t>WO2145789</t>
+  </si>
+  <si>
+    <t>RMA-25204</t>
+  </si>
+  <si>
+    <t>PS02-00-21862</t>
+  </si>
+  <si>
+    <t>WO2145644</t>
+  </si>
+  <si>
+    <t>RMA-25214</t>
+  </si>
+  <si>
+    <t>PS02-02-22334</t>
+  </si>
+  <si>
+    <t>WO2145852</t>
+  </si>
+  <si>
+    <t>RMA-25246</t>
+  </si>
+  <si>
+    <t>PS02-09-24441</t>
+  </si>
+  <si>
+    <t>WO2146070</t>
+  </si>
+  <si>
+    <t>RMA-25275</t>
+  </si>
+  <si>
+    <t>PS02-00-22018</t>
+  </si>
+  <si>
+    <t>WO2146461</t>
+  </si>
+  <si>
+    <t>RMA-25310</t>
+  </si>
+  <si>
+    <t>PS02-01-22100</t>
+  </si>
+  <si>
+    <t>WO2146858</t>
+  </si>
+  <si>
+    <t>RMA-25321</t>
+  </si>
+  <si>
+    <t>PS02-03-22619</t>
+  </si>
+  <si>
+    <t>WO2148017</t>
+  </si>
+  <si>
+    <t>RMA-25360</t>
+  </si>
+  <si>
+    <t>PS02-01-22320</t>
+  </si>
+  <si>
+    <t>WO2148492</t>
+  </si>
+  <si>
+    <t>RMA-25393</t>
+  </si>
+  <si>
+    <t>PS02-99-21859</t>
+  </si>
+  <si>
+    <t>WO2148942</t>
+  </si>
+  <si>
+    <t>RMA-25405</t>
+  </si>
+  <si>
+    <t>PS02-02-22350</t>
+  </si>
+  <si>
+    <t>WO2149123</t>
+  </si>
+  <si>
+    <t>RMA-25430</t>
+  </si>
+  <si>
+    <t>PS02-04-22786</t>
+  </si>
+  <si>
+    <t>WO2149028</t>
+  </si>
+  <si>
+    <t>RMA-25441</t>
+  </si>
+  <si>
+    <t>PS02-00-21948</t>
+  </si>
+  <si>
+    <t>WO2149670</t>
+  </si>
+  <si>
+    <t>RMA-25458</t>
+  </si>
+  <si>
+    <t>PS02-01-22154</t>
+  </si>
+  <si>
+    <t>WO2151888</t>
+  </si>
+  <si>
+    <t>RMA-25468</t>
+  </si>
+  <si>
+    <t>PS02-01-22224</t>
+  </si>
+  <si>
+    <t>WO2152664</t>
+  </si>
+  <si>
+    <t>RMA-25490</t>
+  </si>
+  <si>
+    <t>PS02-99-21604</t>
+  </si>
+  <si>
+    <t>WO2153529</t>
+  </si>
+  <si>
+    <t>RMA-25505</t>
+  </si>
+  <si>
+    <t>PS02-99-21837</t>
+  </si>
+  <si>
+    <t>WO2153712</t>
+  </si>
+  <si>
+    <t>RMA-25518</t>
+  </si>
+  <si>
+    <t>PS02-09-24734</t>
+  </si>
+  <si>
+    <t>WO2154137</t>
+  </si>
+  <si>
+    <t>RMA-25525</t>
+  </si>
+  <si>
+    <t>PS02-00-21879</t>
+  </si>
+  <si>
+    <t>WO2154065</t>
+  </si>
+  <si>
+    <t>RMA-25547</t>
+  </si>
+  <si>
+    <t>PS02-99-21608</t>
+  </si>
+  <si>
+    <t>WO2156290</t>
+  </si>
+  <si>
+    <t>RMA-25568</t>
+  </si>
+  <si>
+    <t>PS02-98-21568</t>
+  </si>
+  <si>
+    <t>WO2157276</t>
+  </si>
+  <si>
+    <t>RMA-25605</t>
+  </si>
+  <si>
+    <t>PS02-16-27154</t>
+  </si>
+  <si>
+    <t>WO2158995</t>
+  </si>
+  <si>
+    <t>RMA-25623</t>
+  </si>
+  <si>
+    <t>PS02-01-22180</t>
+  </si>
+  <si>
+    <t>WO2158849</t>
+  </si>
+  <si>
+    <t>RMA-25632</t>
+  </si>
+  <si>
+    <t>PS02-99-21814</t>
+  </si>
+  <si>
+    <t>WO2159024</t>
   </si>
   <si>
     <t>RMA-25668</t>
   </si>
   <si>
-    <t>PS02-00-21842</t>
-  </si>
-  <si>
-    <t>WO2169720</t>
-  </si>
-  <si>
-    <t>RMA-25700</t>
-  </si>
-  <si>
-    <t>PS02-09-24439</t>
-  </si>
-  <si>
-    <t>WO2169602</t>
-  </si>
-  <si>
-    <t>RMA-25725</t>
-  </si>
-  <si>
-    <t>PS02-03-22344</t>
-  </si>
-  <si>
-    <t>WO2172040</t>
-  </si>
-  <si>
-    <t>RMA-25758</t>
-  </si>
-  <si>
-    <t>PS02-12-25613</t>
-  </si>
-  <si>
-    <t>WO2172633</t>
-  </si>
-  <si>
-    <t>RMA-25778</t>
-  </si>
-  <si>
-    <t>PS02-03-22357</t>
-  </si>
-  <si>
-    <t>WO2173388</t>
+    <t>PS02-02-22436</t>
+  </si>
+  <si>
+    <t>WO2159350</t>
+  </si>
+  <si>
+    <t>RMA-25705</t>
+  </si>
+  <si>
+    <t>PS02-01-22308</t>
+  </si>
+  <si>
+    <t>WO2159799</t>
+  </si>
+  <si>
+    <t>RMA-25741</t>
+  </si>
+  <si>
+    <t>PS02-09-24469</t>
+  </si>
+  <si>
+    <t>WO2160718</t>
+  </si>
+  <si>
+    <t>RMA-25748</t>
+  </si>
+  <si>
+    <t>PS02-06-23228</t>
+  </si>
+  <si>
+    <t>WO2164217</t>
+  </si>
+  <si>
+    <t>RMA-25765</t>
+  </si>
+  <si>
+    <t>PS02-08-24195</t>
+  </si>
+  <si>
+    <t>WO2164474</t>
+  </si>
+  <si>
+    <t>RMA-25802</t>
+  </si>
+  <si>
+    <t>PS02-07-23728</t>
+  </si>
+  <si>
+    <t>WO2164906</t>
   </si>
   <si>
     <t>RMA-25809</t>
   </si>
   <si>
-    <t>PS02-04-22622</t>
-  </si>
-  <si>
-    <t>WO2174994</t>
-  </si>
-  <si>
-    <t>RMA-25825</t>
-  </si>
-  <si>
-    <t>PS02-07-23356</t>
-  </si>
-  <si>
-    <t>WO2175520</t>
-  </si>
-  <si>
-    <t>RMA-25858</t>
-  </si>
-  <si>
-    <t>PS02-10-24553</t>
-  </si>
-  <si>
-    <t>WO2176313</t>
-  </si>
-  <si>
-    <t>RMA-25877</t>
-  </si>
-  <si>
-    <t>PS02-12-25484</t>
-  </si>
-  <si>
-    <t>WO2177746</t>
-  </si>
-  <si>
-    <t>RMA-25900</t>
-  </si>
-  <si>
-    <t>PS02-11-25096</t>
-  </si>
-  <si>
-    <t>WO2178803</t>
-  </si>
-  <si>
-    <t>RMA-25926</t>
-  </si>
-  <si>
-    <t>PS02-13-25814</t>
-  </si>
-  <si>
-    <t>WO2179049</t>
-  </si>
-  <si>
-    <t>RMA-25960</t>
-  </si>
-  <si>
-    <t>PS02-15-26747</t>
-  </si>
-  <si>
-    <t>WO2179325</t>
-  </si>
-  <si>
-    <t>RMA-25996</t>
-  </si>
-  <si>
-    <t>PS02-10-24662</t>
-  </si>
-  <si>
-    <t>WO2180152</t>
-  </si>
-  <si>
-    <t>RMA-26032</t>
-  </si>
-  <si>
-    <t>PS02-00-21694</t>
-  </si>
-  <si>
-    <t>WO2180307</t>
-  </si>
-  <si>
-    <t>RMA-26065</t>
-  </si>
-  <si>
-    <t>PS02-11-25279</t>
-  </si>
-  <si>
-    <t>WO2180637</t>
-  </si>
-  <si>
-    <t>RMA-26103</t>
-  </si>
-  <si>
-    <t>PS02-11-25163</t>
-  </si>
-  <si>
-    <t>WO2181885</t>
-  </si>
-  <si>
-    <t>RMA-26130</t>
-  </si>
-  <si>
-    <t>PS02-10-24636</t>
-  </si>
-  <si>
-    <t>WO2182997</t>
-  </si>
-  <si>
-    <t>RMA-26155</t>
-  </si>
-  <si>
-    <t>PS02-08-24034</t>
-  </si>
-  <si>
-    <t>WO2183316</t>
-  </si>
-  <si>
-    <t>RMA-26164</t>
-  </si>
-  <si>
-    <t>PS02-00-21627</t>
-  </si>
-  <si>
-    <t>WO2183421</t>
-  </si>
-  <si>
-    <t>RMA-26189</t>
-  </si>
-  <si>
-    <t>PS02-98-21478</t>
-  </si>
-  <si>
-    <t>WO2183511</t>
-  </si>
-  <si>
-    <t>RMA-26206</t>
-  </si>
-  <si>
-    <t>PS02-07-23200</t>
-  </si>
-  <si>
-    <t>WO2186392</t>
-  </si>
-  <si>
-    <t>RMA-26235</t>
-  </si>
-  <si>
-    <t>PS02-02-22113</t>
-  </si>
-  <si>
-    <t>WO2186588</t>
-  </si>
-  <si>
-    <t>RMA-26272</t>
-  </si>
-  <si>
-    <t>PS02-08-23952</t>
-  </si>
-  <si>
-    <t>WO2186699</t>
-  </si>
-  <si>
-    <t>RMA-26292</t>
-  </si>
-  <si>
-    <t>PS02-07-23251</t>
-  </si>
-  <si>
-    <t>WO2187184</t>
-  </si>
-  <si>
-    <t>RMA-26303</t>
-  </si>
-  <si>
-    <t>PS02-02-22158</t>
-  </si>
-  <si>
-    <t>WO2190763</t>
-  </si>
-  <si>
-    <t>RMA-26331</t>
-  </si>
-  <si>
-    <t>PS02-00-21646</t>
-  </si>
-  <si>
-    <t>WO2192669</t>
-  </si>
-  <si>
-    <t>RMA-26342</t>
-  </si>
-  <si>
-    <t>PS02-02-22120</t>
-  </si>
-  <si>
-    <t>WO2192895</t>
-  </si>
-  <si>
-    <t>RMA-26374</t>
-  </si>
-  <si>
-    <t>PS02-02-22336</t>
-  </si>
-  <si>
-    <t>WO2193649</t>
-  </si>
-  <si>
-    <t>RMA-26383</t>
-  </si>
-  <si>
-    <t>PS02-03-22436</t>
-  </si>
-  <si>
-    <t>WO2194027</t>
-  </si>
-  <si>
-    <t>RMA-26410</t>
-  </si>
-  <si>
-    <t>PS02-00-21839</t>
-  </si>
-  <si>
-    <t>WO2194307</t>
-  </si>
-  <si>
-    <t>RMA-26432</t>
-  </si>
-  <si>
-    <t>PS02-09-24354</t>
-  </si>
-  <si>
-    <t>WO2194667</t>
-  </si>
-  <si>
-    <t>RMA-26459</t>
-  </si>
-  <si>
-    <t>PS02-12-25316</t>
-  </si>
-  <si>
-    <t>WO2195501</t>
-  </si>
-  <si>
-    <t>RMA-26474</t>
-  </si>
-  <si>
-    <t>PS02-98-21486</t>
-  </si>
-  <si>
-    <t>WO2195620</t>
-  </si>
-  <si>
-    <t>RMA-26504</t>
-  </si>
-  <si>
-    <t>PS02-05-22799</t>
-  </si>
-  <si>
-    <t>WO2195719</t>
-  </si>
-  <si>
-    <t>RMA-26524</t>
-  </si>
-  <si>
-    <t>PS02-03-22396</t>
-  </si>
-  <si>
-    <t>WO2196463</t>
-  </si>
-  <si>
-    <t>RMA-26540</t>
-  </si>
-  <si>
-    <t>PS02-02-22161</t>
-  </si>
-  <si>
-    <t>WO2196992</t>
-  </si>
-  <si>
-    <t>RMA-26551</t>
-  </si>
-  <si>
-    <t>PS02-00-21787</t>
-  </si>
-  <si>
-    <t>WO2197312</t>
-  </si>
-  <si>
-    <t>RMA-26557</t>
-  </si>
-  <si>
-    <t>PS02-04-22661</t>
-  </si>
-  <si>
-    <t>WO2199826</t>
-  </si>
-  <si>
-    <t>RMA-26564</t>
-  </si>
-  <si>
-    <t>PS02-00-21831</t>
-  </si>
-  <si>
-    <t>WO2200119</t>
-  </si>
-  <si>
-    <t>RMA-26585</t>
-  </si>
-  <si>
-    <t>PS02-04-22472</t>
-  </si>
-  <si>
-    <t>WO2200219</t>
-  </si>
-  <si>
-    <t>RMA-26596</t>
-  </si>
-  <si>
-    <t>PS02-13-25936</t>
-  </si>
-  <si>
-    <t>WO2200584</t>
-  </si>
-  <si>
-    <t>RMA-26608</t>
-  </si>
-  <si>
-    <t>PS02-00-21689</t>
-  </si>
-  <si>
-    <t>WO2201707</t>
-  </si>
-  <si>
-    <t>RMA-26615</t>
-  </si>
-  <si>
-    <t>PS02-03-22458</t>
-  </si>
-  <si>
-    <t>WO2203453</t>
-  </si>
-  <si>
-    <t>RMA-26646</t>
-  </si>
-  <si>
-    <t>PS02-03-22361</t>
-  </si>
-  <si>
-    <t>WO2203964</t>
+    <t>PS02-06-23363</t>
+  </si>
+  <si>
+    <t>WO2165014</t>
+  </si>
+  <si>
+    <t>RMA-25834</t>
+  </si>
+  <si>
+    <t>PS02-07-23513</t>
+  </si>
+  <si>
+    <t>WO2165342</t>
+  </si>
+  <si>
+    <t>RMA-25853</t>
+  </si>
+  <si>
+    <t>PS02-02-22343</t>
+  </si>
+  <si>
+    <t>WO2165885</t>
+  </si>
+  <si>
+    <t>RMA-25874</t>
+  </si>
+  <si>
+    <t>PS02-09-24592</t>
+  </si>
+  <si>
+    <t>WO2167062</t>
+  </si>
+  <si>
+    <t>RMA-25880</t>
+  </si>
+  <si>
+    <t>PS02-10-25074</t>
+  </si>
+  <si>
+    <t>WO2167915</t>
+  </si>
+  <si>
+    <t>RMA-25897</t>
+  </si>
+  <si>
+    <t>PS02-09-24654</t>
+  </si>
+  <si>
+    <t>WO2169681</t>
+  </si>
+  <si>
+    <t>RMA-25924</t>
+  </si>
+  <si>
+    <t>PS02-99-21819</t>
+  </si>
+  <si>
+    <t>WO2170112</t>
+  </si>
+  <si>
+    <t>RMA-25949</t>
+  </si>
+  <si>
+    <t>PS02-02-22463</t>
+  </si>
+  <si>
+    <t>WO2172339</t>
+  </si>
+  <si>
+    <t>RMA-25968</t>
+  </si>
+  <si>
+    <t>PS02-12-25623</t>
+  </si>
+  <si>
+    <t>WO2173326</t>
+  </si>
+  <si>
+    <t>RMA-25995</t>
+  </si>
+  <si>
+    <t>PS02-07-23413</t>
+  </si>
+  <si>
+    <t>WO2174449</t>
+  </si>
+  <si>
+    <t>RMA-26035</t>
+  </si>
+  <si>
+    <t>PS02-01-22150</t>
+  </si>
+  <si>
+    <t>WO2174671</t>
+  </si>
+  <si>
+    <t>RMA-26049</t>
+  </si>
+  <si>
+    <t>PS02-07-23506</t>
+  </si>
+  <si>
+    <t>WO2175624</t>
+  </si>
+  <si>
+    <t>RMA-26072</t>
+  </si>
+  <si>
+    <t>PS02-07-23524</t>
+  </si>
+  <si>
+    <t>WO2176143</t>
+  </si>
+  <si>
+    <t>RMA-26088</t>
+  </si>
+  <si>
+    <t>PS02-12-25704</t>
+  </si>
+  <si>
+    <t>WO2176845</t>
+  </si>
+  <si>
+    <t>RMA-26104</t>
+  </si>
+  <si>
+    <t>PS02-08-24233</t>
+  </si>
+  <si>
+    <t>WO2177222</t>
+  </si>
+  <si>
+    <t>RMA-26136</t>
+  </si>
+  <si>
+    <t>PS02-99-21759</t>
+  </si>
+  <si>
+    <t>WO2178027</t>
+  </si>
+  <si>
+    <t>RMA-26167</t>
+  </si>
+  <si>
+    <t>PS02-09-24405</t>
+  </si>
+  <si>
+    <t>WO2178825</t>
+  </si>
+  <si>
+    <t>RMA-26199</t>
+  </si>
+  <si>
+    <t>PS02-08-24332</t>
+  </si>
+  <si>
+    <t>WO2179048</t>
+  </si>
+  <si>
+    <t>RMA-26211</t>
+  </si>
+  <si>
+    <t>PS02-10-25172</t>
+  </si>
+  <si>
+    <t>WO2180038</t>
+  </si>
+  <si>
+    <t>RMA-26246</t>
+  </si>
+  <si>
+    <t>PS02-12-25856</t>
+  </si>
+  <si>
+    <t>WO2180430</t>
+  </si>
+  <si>
+    <t>RMA-26263</t>
+  </si>
+  <si>
+    <t>PS02-15-26931</t>
+  </si>
+  <si>
+    <t>WO2181085</t>
+  </si>
+  <si>
+    <t>RMA-26299</t>
+  </si>
+  <si>
+    <t>PS02-12-25945</t>
+  </si>
+  <si>
+    <t>WO2181590</t>
+  </si>
+  <si>
+    <t>RMA-26333</t>
+  </si>
+  <si>
+    <t>PS02-04-22725</t>
+  </si>
+  <si>
+    <t>WO2181666</t>
+  </si>
+  <si>
+    <t>RMA-26351</t>
+  </si>
+  <si>
+    <t>PS02-00-21974</t>
+  </si>
+  <si>
+    <t>WO2181958</t>
+  </si>
+  <si>
+    <t>RMA-26362</t>
+  </si>
+  <si>
+    <t>PS02-09-24598</t>
+  </si>
+  <si>
+    <t>WO2182306</t>
+  </si>
+  <si>
+    <t>RMA-26373</t>
+  </si>
+  <si>
+    <t>PS02-00-21988</t>
+  </si>
+  <si>
+    <t>WO2182324</t>
+  </si>
+  <si>
+    <t>RMA-26398</t>
+  </si>
+  <si>
+    <t>PS02-11-25384</t>
+  </si>
+  <si>
+    <t>WO2183147</t>
+  </si>
+  <si>
+    <t>RMA-26429</t>
+  </si>
+  <si>
+    <t>PS02-10-25195</t>
+  </si>
+  <si>
+    <t>WO2183464</t>
+  </si>
+  <si>
+    <t>RMA-26438</t>
+  </si>
+  <si>
+    <t>PS02-01-22170</t>
+  </si>
+  <si>
+    <t>WO2188137</t>
+  </si>
+  <si>
+    <t>RMA-26460</t>
+  </si>
+  <si>
+    <t>PS02-06-23364</t>
+  </si>
+  <si>
+    <t>WO2188462</t>
+  </si>
+  <si>
+    <t>RMA-26486</t>
+  </si>
+  <si>
+    <t>PS02-06-23293</t>
+  </si>
+  <si>
+    <t>WO2188896</t>
+  </si>
+  <si>
+    <t>RMA-26501</t>
+  </si>
+  <si>
+    <t>PS02-07-23891</t>
+  </si>
+  <si>
+    <t>WO2188959</t>
+  </si>
+  <si>
+    <t>RMA-26523</t>
+  </si>
+  <si>
+    <t>PS02-04-22734</t>
+  </si>
+  <si>
+    <t>WO2191275</t>
+  </si>
+  <si>
+    <t>RMA-26563</t>
+  </si>
+  <si>
+    <t>PS02-98-21577</t>
+  </si>
+  <si>
+    <t>WO2192311</t>
+  </si>
+  <si>
+    <t>RMA-26572</t>
+  </si>
+  <si>
+    <t>PS02-02-22362</t>
+  </si>
+  <si>
+    <t>WO2192787</t>
+  </si>
+  <si>
+    <t>RMA-26593</t>
+  </si>
+  <si>
+    <t>PS02-11-25620</t>
+  </si>
+  <si>
+    <t>WO2193259</t>
+  </si>
+  <si>
+    <t>RMA-26621</t>
+  </si>
+  <si>
+    <t>PS02-99-21842</t>
+  </si>
+  <si>
+    <t>WO2194769</t>
+  </si>
+  <si>
+    <t>RMA-26656</t>
+  </si>
+  <si>
+    <t>PS02-02-22481</t>
+  </si>
+  <si>
+    <t>WO2195428</t>
   </si>
   <si>
     <t>RMA-26678</t>
   </si>
   <si>
-    <t>PS02-16-26878</t>
-  </si>
-  <si>
-    <t>WO2205542</t>
-  </si>
-  <si>
-    <t>RMA-26718</t>
-  </si>
-  <si>
-    <t>PS02-02-22267</t>
-  </si>
-  <si>
-    <t>WO2209112</t>
+    <t>PS02-00-21924</t>
+  </si>
+  <si>
+    <t>WO2196196</t>
+  </si>
+  <si>
+    <t>RMA-26705</t>
+  </si>
+  <si>
+    <t>PS02-09-24622</t>
+  </si>
+  <si>
+    <t>WO2198203</t>
+  </si>
+  <si>
+    <t>RMA-26725</t>
+  </si>
+  <si>
+    <t>PS02-98-21547</t>
+  </si>
+  <si>
+    <t>WO2198333</t>
+  </si>
+  <si>
+    <t>RMA-26744</t>
+  </si>
+  <si>
+    <t>PS02-99-21808</t>
+  </si>
+  <si>
+    <t>WO2198532</t>
+  </si>
+  <si>
+    <t>RMA-26754</t>
+  </si>
+  <si>
+    <t>PS02-03-22542</t>
+  </si>
+  <si>
+    <t>WO2199260</t>
+  </si>
+  <si>
+    <t>RMA-26767</t>
+  </si>
+  <si>
+    <t>PS02-10-24903</t>
+  </si>
+  <si>
+    <t>WO2202341</t>
+  </si>
+  <si>
+    <t>RMA-26778</t>
+  </si>
+  <si>
+    <t>PS02-00-22072</t>
+  </si>
+  <si>
+    <t>WO2202348</t>
+  </si>
+  <si>
+    <t>RMA-26814</t>
+  </si>
+  <si>
+    <t>PS02-04-22830</t>
+  </si>
+  <si>
+    <t>WO2202347</t>
+  </si>
+  <si>
+    <t>RMA-26830</t>
+  </si>
+  <si>
+    <t>PS02-13-26085</t>
+  </si>
+  <si>
+    <t>WO2202346</t>
+  </si>
+  <si>
+    <t>RMA-26861</t>
+  </si>
+  <si>
+    <t>PS02-09-24714</t>
+  </si>
+  <si>
+    <t>WO2203063</t>
+  </si>
+  <si>
+    <t>RMA-26882</t>
+  </si>
+  <si>
+    <t>PS02-99-21786</t>
+  </si>
+  <si>
+    <t>WO2204214</t>
+  </si>
+  <si>
+    <t>RMA-26922</t>
+  </si>
+  <si>
+    <t>PS02-04-22747</t>
+  </si>
+  <si>
+    <t>WO2204977</t>
+  </si>
+  <si>
+    <t>RMA-26957</t>
+  </si>
+  <si>
+    <t>PS02-02-22499</t>
+  </si>
+  <si>
+    <t>WO2206844</t>
+  </si>
+  <si>
+    <t>RMA-26980</t>
+  </si>
+  <si>
+    <t>PS02-07-23429</t>
+  </si>
+  <si>
+    <t>WO2207385</t>
+  </si>
+  <si>
+    <t>RMA-26988</t>
+  </si>
+  <si>
+    <t>PS02-10-24954</t>
+  </si>
+  <si>
+    <t>WO2207834</t>
+  </si>
+  <si>
+    <t>RMA-27006</t>
+  </si>
+  <si>
+    <t>PS02-01-22285</t>
+  </si>
+  <si>
+    <t>WO2212965</t>
+  </si>
+  <si>
+    <t>RMA-27031</t>
+  </si>
+  <si>
+    <t>PS02-11-25564</t>
+  </si>
+  <si>
+    <t>WO2213017</t>
+  </si>
+  <si>
+    <t>RMA-27054</t>
+  </si>
+  <si>
+    <t>PS02-04-22766</t>
+  </si>
+  <si>
+    <t>WO2213931</t>
   </si>
   <si>
     <t>OPEN</t>
   </si>
   <si>
-    <t>RMA-26756</t>
-  </si>
-  <si>
-    <t>PS02-00-21914</t>
-  </si>
-  <si>
-    <t>WO2209470</t>
-  </si>
-  <si>
-    <t>RMA-26792</t>
-  </si>
-  <si>
-    <t>PS02-00-21772</t>
-  </si>
-  <si>
-    <t>WO2209774</t>
-  </si>
-  <si>
-    <t>RMA-26830</t>
-  </si>
-  <si>
-    <t>PS02-12-25296</t>
-  </si>
-  <si>
-    <t>WO2209813</t>
-  </si>
-  <si>
-    <t>RMA-26869</t>
-  </si>
-  <si>
-    <t>PS02-07-23222</t>
-  </si>
-  <si>
-    <t>WO2210581</t>
+    <t>RMA-27072</t>
+  </si>
+  <si>
+    <t>PS02-15-26835</t>
+  </si>
+  <si>
+    <t>WO2215082</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mmm-yyyy"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -1112,82 +1258,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
@@ -1202,44 +1284,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="44546A"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E7E6E6"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4472C4"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="ED7D31"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A5A5A5"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="FFC000"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="5B9BD5"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="70AD47"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0563C1"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1268,12 +1350,12 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游明朝"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1475,41 +1557,47 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H114"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAAB4F5D-AE64-4098-BAC9-2AE0ABCA5137}">
+  <dimension ref="A1:H129"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1525,17 +1613,17 @@
       <c r="E2" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="1" t="n">
-        <v>44213</v>
+      <c r="F2" s="2">
+        <v>44214</v>
       </c>
       <c r="G2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="1" t="n">
-        <v>44282</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="H2" s="2">
+        <v>44272</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1551,17 +1639,17 @@
       <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="1" t="n">
-        <v>44222</v>
+      <c r="F3" s="2">
+        <v>44236</v>
       </c>
       <c r="G3" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="1" t="n">
-        <v>44285</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="H3" s="2">
+        <v>44287</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>17</v>
       </c>
@@ -1577,17 +1665,17 @@
       <c r="E4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="1" t="n">
-        <v>44232</v>
+      <c r="F4" s="2">
+        <v>44273</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="1" t="n">
-        <v>44285</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="H4" s="2">
+        <v>44342</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1603,17 +1691,17 @@
       <c r="E5" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>44306</v>
+      <c r="F5" s="2">
+        <v>44286</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>44376</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="H5" s="2">
+        <v>44323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>23</v>
       </c>
@@ -1629,14 +1717,14 @@
       <c r="E6" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="1" t="n">
-        <v>44355</v>
+      <c r="F6" s="2">
+        <v>44307</v>
       </c>
       <c r="G6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1652,17 +1740,17 @@
       <c r="E7" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="1" t="n">
-        <v>44383</v>
+      <c r="F7" s="2">
+        <v>44334</v>
       </c>
       <c r="G7" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="1" t="n">
-        <v>44432</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="H7" s="2">
+        <v>44371</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>30</v>
       </c>
@@ -1678,14 +1766,17 @@
       <c r="E8" t="s">
         <v>32</v>
       </c>
-      <c r="F8" s="1" t="n">
-        <v>44412</v>
+      <c r="F8" s="2">
+        <v>44337</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>13</v>
+      </c>
+      <c r="H8" s="2">
+        <v>44384</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>33</v>
       </c>
@@ -1701,17 +1792,17 @@
       <c r="E9" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="1" t="n">
-        <v>44437</v>
+      <c r="F9" s="2">
+        <v>44348</v>
       </c>
       <c r="G9" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="1" t="n">
-        <v>44507</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="H9" s="2">
+        <v>44417</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -1727,14 +1818,17 @@
       <c r="E10" t="s">
         <v>38</v>
       </c>
-      <c r="F10" s="1" t="n">
-        <v>44445</v>
+      <c r="F10" s="2">
+        <v>44361</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2">
+        <v>44405</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>39</v>
       </c>
@@ -1750,17 +1844,17 @@
       <c r="E11" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="1" t="n">
-        <v>44489</v>
+      <c r="F11" s="2">
+        <v>44365</v>
       </c>
       <c r="G11" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="1" t="n">
-        <v>44546</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="H11" s="2">
+        <v>44424</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>42</v>
       </c>
@@ -1776,17 +1870,17 @@
       <c r="E12" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="1" t="n">
-        <v>44508</v>
+      <c r="F12" s="2">
+        <v>44377</v>
       </c>
       <c r="G12" t="s">
         <v>13</v>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>44558</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="H12" s="2">
+        <v>44426</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1802,17 +1896,14 @@
       <c r="E13" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="1" t="n">
-        <v>44513</v>
+      <c r="F13" s="2">
+        <v>44406</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
-      </c>
-      <c r="H13" s="1" t="n">
-        <v>44556</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>48</v>
       </c>
@@ -1828,17 +1919,17 @@
       <c r="E14" t="s">
         <v>50</v>
       </c>
-      <c r="F14" s="1" t="n">
-        <v>44516</v>
+      <c r="F14" s="2">
+        <v>44432</v>
       </c>
       <c r="G14" t="s">
         <v>13</v>
       </c>
-      <c r="H14" s="1" t="n">
-        <v>44576</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="H14" s="2">
+        <v>44467</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>51</v>
       </c>
@@ -1854,14 +1945,17 @@
       <c r="E15" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="1" t="n">
-        <v>44530</v>
+      <c r="F15" s="2">
+        <v>44434</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>13</v>
+      </c>
+      <c r="H15" s="2">
+        <v>44463</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -1877,14 +1971,17 @@
       <c r="E16" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="1" t="n">
-        <v>44541</v>
+      <c r="F16" s="2">
+        <v>44442</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>13</v>
+      </c>
+      <c r="H16" s="2">
+        <v>44484</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -1900,14 +1997,17 @@
       <c r="E17" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="1" t="n">
-        <v>44547</v>
+      <c r="F17" s="2">
+        <v>44504</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>13</v>
+      </c>
+      <c r="H17" s="2">
+        <v>44537</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>60</v>
       </c>
@@ -1923,17 +2023,17 @@
       <c r="E18" t="s">
         <v>62</v>
       </c>
-      <c r="F18" s="1" t="n">
-        <v>44551</v>
+      <c r="F18" s="2">
+        <v>44505</v>
       </c>
       <c r="G18" t="s">
         <v>63</v>
       </c>
-      <c r="H18" s="1" t="n">
-        <v>44605</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="H18" s="2">
+        <v>44554</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>64</v>
       </c>
@@ -1949,14 +2049,14 @@
       <c r="E19" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="1" t="n">
-        <v>44587</v>
+      <c r="F19" s="2">
+        <v>44510</v>
       </c>
       <c r="G19" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -1972,17 +2072,17 @@
       <c r="E20" t="s">
         <v>69</v>
       </c>
-      <c r="F20" s="1" t="n">
-        <v>44637</v>
+      <c r="F20" s="2">
+        <v>44540</v>
       </c>
       <c r="G20" t="s">
         <v>13</v>
       </c>
-      <c r="H20" s="1" t="n">
-        <v>44709</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="H20" s="2">
+        <v>44596</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>70</v>
       </c>
@@ -1998,17 +2098,17 @@
       <c r="E21" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="1" t="n">
-        <v>44638</v>
+      <c r="F21" s="2">
+        <v>44540</v>
       </c>
       <c r="G21" t="s">
         <v>13</v>
       </c>
-      <c r="H21" s="1" t="n">
-        <v>44669</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="H21" s="2">
+        <v>44599</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -2024,17 +2124,17 @@
       <c r="E22" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="1" t="n">
-        <v>44705</v>
+      <c r="F22" s="2">
+        <v>44547</v>
       </c>
       <c r="G22" t="s">
-        <v>13</v>
-      </c>
-      <c r="H22" s="1" t="n">
-        <v>44769</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>63</v>
+      </c>
+      <c r="H22" s="2">
+        <v>44609</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>76</v>
       </c>
@@ -2050,17 +2150,17 @@
       <c r="E23" t="s">
         <v>78</v>
       </c>
-      <c r="F23" s="1" t="n">
-        <v>44715</v>
+      <c r="F23" s="2">
+        <v>44603</v>
       </c>
       <c r="G23" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="1" t="n">
-        <v>44746</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="H23" s="2">
+        <v>44678</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>79</v>
       </c>
@@ -2076,17 +2176,17 @@
       <c r="E24" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="1" t="n">
-        <v>44731</v>
+      <c r="F24" s="2">
+        <v>44644</v>
       </c>
       <c r="G24" t="s">
         <v>13</v>
       </c>
-      <c r="H24" s="1" t="n">
-        <v>44802</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="H24" s="2">
+        <v>44711</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>82</v>
       </c>
@@ -2102,17 +2202,14 @@
       <c r="E25" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="1" t="n">
-        <v>44740</v>
+      <c r="F25" s="2">
+        <v>44662</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>44805</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>85</v>
       </c>
@@ -2128,14 +2225,17 @@
       <c r="E26" t="s">
         <v>87</v>
       </c>
-      <c r="F26" s="1" t="n">
-        <v>44745</v>
+      <c r="F26" s="2">
+        <v>44671</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>13</v>
+      </c>
+      <c r="H26" s="2">
+        <v>44712</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>88</v>
       </c>
@@ -2151,17 +2251,17 @@
       <c r="E27" t="s">
         <v>90</v>
       </c>
-      <c r="F27" s="1" t="n">
-        <v>44762</v>
+      <c r="F27" s="2">
+        <v>44701</v>
       </c>
       <c r="G27" t="s">
         <v>13</v>
       </c>
-      <c r="H27" s="1" t="n">
-        <v>44800</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="H27" s="2">
+        <v>44757</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>91</v>
       </c>
@@ -2177,17 +2277,17 @@
       <c r="E28" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="1" t="n">
-        <v>44762</v>
+      <c r="F28" s="2">
+        <v>44708</v>
       </c>
       <c r="G28" t="s">
         <v>13</v>
       </c>
-      <c r="H28" s="1" t="n">
-        <v>44802</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="H28" s="2">
+        <v>44774</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>94</v>
       </c>
@@ -2203,17 +2303,17 @@
       <c r="E29" t="s">
         <v>96</v>
       </c>
-      <c r="F29" s="1" t="n">
-        <v>44841</v>
+      <c r="F29" s="2">
+        <v>44712</v>
       </c>
       <c r="G29" t="s">
         <v>13</v>
       </c>
-      <c r="H29" s="1" t="n">
-        <v>44887</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="H29" s="2">
+        <v>44750</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -2229,17 +2329,17 @@
       <c r="E30" t="s">
         <v>99</v>
       </c>
-      <c r="F30" s="1" t="n">
-        <v>44853</v>
+      <c r="F30" s="2">
+        <v>44732</v>
       </c>
       <c r="G30" t="s">
         <v>13</v>
       </c>
-      <c r="H30" s="1" t="n">
-        <v>44914</v>
-      </c>
-    </row>
-    <row r="31">
+      <c r="H30" s="2">
+        <v>44803</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>100</v>
       </c>
@@ -2255,17 +2355,17 @@
       <c r="E31" t="s">
         <v>102</v>
       </c>
-      <c r="F31" s="1" t="n">
-        <v>44859</v>
+      <c r="F31" s="2">
+        <v>44732</v>
       </c>
       <c r="G31" t="s">
         <v>13</v>
       </c>
-      <c r="H31" s="1" t="n">
-        <v>44914</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="H31" s="2">
+        <v>44770</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>103</v>
       </c>
@@ -2281,17 +2381,17 @@
       <c r="E32" t="s">
         <v>105</v>
       </c>
-      <c r="F32" s="1" t="n">
-        <v>44884</v>
+      <c r="F32" s="2">
+        <v>44739</v>
       </c>
       <c r="G32" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="1" t="n">
-        <v>44941</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="H32" s="2">
+        <v>44811</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>106</v>
       </c>
@@ -2307,14 +2407,17 @@
       <c r="E33" t="s">
         <v>108</v>
       </c>
-      <c r="F33" s="1" t="n">
-        <v>44901</v>
+      <c r="F33" s="2">
+        <v>44746</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34">
+        <v>13</v>
+      </c>
+      <c r="H33" s="2">
+        <v>44805</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>109</v>
       </c>
@@ -2330,17 +2433,17 @@
       <c r="E34" t="s">
         <v>111</v>
       </c>
-      <c r="F34" s="1" t="n">
-        <v>44912</v>
+      <c r="F34" s="2">
+        <v>44763</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>44957</v>
-      </c>
-    </row>
-    <row r="35">
+        <v>63</v>
+      </c>
+      <c r="H34" s="2">
+        <v>44834</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>112</v>
       </c>
@@ -2356,17 +2459,17 @@
       <c r="E35" t="s">
         <v>114</v>
       </c>
-      <c r="F35" s="1" t="n">
-        <v>44934</v>
+      <c r="F35" s="2">
+        <v>44825</v>
       </c>
       <c r="G35" t="s">
         <v>13</v>
       </c>
-      <c r="H35" s="1" t="n">
-        <v>44983</v>
-      </c>
-    </row>
-    <row r="36">
+      <c r="H35" s="2">
+        <v>44859</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>115</v>
       </c>
@@ -2382,14 +2485,17 @@
       <c r="E36" t="s">
         <v>117</v>
       </c>
-      <c r="F36" s="1" t="n">
-        <v>44989</v>
+      <c r="F36" s="2">
+        <v>44852</v>
       </c>
       <c r="G36" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37">
+        <v>13</v>
+      </c>
+      <c r="H36" s="2">
+        <v>44917</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>118</v>
       </c>
@@ -2405,17 +2511,17 @@
       <c r="E37" t="s">
         <v>120</v>
       </c>
-      <c r="F37" s="1" t="n">
-        <v>44999</v>
+      <c r="F37" s="2">
+        <v>44865</v>
       </c>
       <c r="G37" t="s">
         <v>13</v>
       </c>
-      <c r="H37" s="1" t="n">
-        <v>45064</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="H37" s="2">
+        <v>44896</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>121</v>
       </c>
@@ -2431,14 +2537,17 @@
       <c r="E38" t="s">
         <v>123</v>
       </c>
-      <c r="F38" s="1" t="n">
-        <v>45002</v>
+      <c r="F38" s="2">
+        <v>44881</v>
       </c>
       <c r="G38" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39">
+        <v>13</v>
+      </c>
+      <c r="H38" s="2">
+        <v>44917</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>124</v>
       </c>
@@ -2454,17 +2563,17 @@
       <c r="E39" t="s">
         <v>126</v>
       </c>
-      <c r="F39" s="1" t="n">
-        <v>45013</v>
+      <c r="F39" s="2">
+        <v>44910</v>
       </c>
       <c r="G39" t="s">
         <v>13</v>
       </c>
-      <c r="H39" s="1" t="n">
-        <v>45055</v>
-      </c>
-    </row>
-    <row r="40">
+      <c r="H39" s="2">
+        <v>44942</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>127</v>
       </c>
@@ -2480,17 +2589,17 @@
       <c r="E40" t="s">
         <v>129</v>
       </c>
-      <c r="F40" s="1" t="n">
-        <v>45014</v>
+      <c r="F40" s="2">
+        <v>44914</v>
       </c>
       <c r="G40" t="s">
         <v>13</v>
       </c>
-      <c r="H40" s="1" t="n">
-        <v>45088</v>
-      </c>
-    </row>
-    <row r="41">
+      <c r="H40" s="2">
+        <v>44971</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>130</v>
       </c>
@@ -2506,17 +2615,17 @@
       <c r="E41" t="s">
         <v>132</v>
       </c>
-      <c r="F41" s="1" t="n">
-        <v>45034</v>
+      <c r="F41" s="2">
+        <v>44925</v>
       </c>
       <c r="G41" t="s">
         <v>13</v>
       </c>
-      <c r="H41" s="1" t="n">
-        <v>45090</v>
-      </c>
-    </row>
-    <row r="42">
+      <c r="H41" s="2">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>133</v>
       </c>
@@ -2532,17 +2641,17 @@
       <c r="E42" t="s">
         <v>135</v>
       </c>
-      <c r="F42" s="1" t="n">
-        <v>45046</v>
+      <c r="F42" s="2">
+        <v>44929</v>
       </c>
       <c r="G42" t="s">
         <v>13</v>
       </c>
-      <c r="H42" s="1" t="n">
-        <v>45107</v>
-      </c>
-    </row>
-    <row r="43">
+      <c r="H42" s="2">
+        <v>44957</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>136</v>
       </c>
@@ -2558,17 +2667,17 @@
       <c r="E43" t="s">
         <v>138</v>
       </c>
-      <c r="F43" s="1" t="n">
-        <v>45060</v>
+      <c r="F43" s="2">
+        <v>44980</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
-      </c>
-      <c r="H43" s="1" t="n">
-        <v>45100</v>
-      </c>
-    </row>
-    <row r="44">
+        <v>13</v>
+      </c>
+      <c r="H43" s="2">
+        <v>45035</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>139</v>
       </c>
@@ -2584,14 +2693,14 @@
       <c r="E44" t="s">
         <v>141</v>
       </c>
-      <c r="F44" s="1" t="n">
-        <v>45102</v>
+      <c r="F44" s="2">
+        <v>44992</v>
       </c>
       <c r="G44" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>142</v>
       </c>
@@ -2607,17 +2716,17 @@
       <c r="E45" t="s">
         <v>144</v>
       </c>
-      <c r="F45" s="1" t="n">
-        <v>45119</v>
+      <c r="F45" s="2">
+        <v>44993</v>
       </c>
       <c r="G45" t="s">
         <v>13</v>
       </c>
-      <c r="H45" s="1" t="n">
-        <v>45146</v>
-      </c>
-    </row>
-    <row r="46">
+      <c r="H45" s="2">
+        <v>45050</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>145</v>
       </c>
@@ -2633,17 +2742,17 @@
       <c r="E46" t="s">
         <v>147</v>
       </c>
-      <c r="F46" s="1" t="n">
-        <v>45119</v>
+      <c r="F46" s="2">
+        <v>44993</v>
       </c>
       <c r="G46" t="s">
         <v>13</v>
       </c>
-      <c r="H46" s="1" t="n">
-        <v>45148</v>
-      </c>
-    </row>
-    <row r="47">
+      <c r="H46" s="2">
+        <v>45064</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>148</v>
       </c>
@@ -2659,17 +2768,14 @@
       <c r="E47" t="s">
         <v>150</v>
       </c>
-      <c r="F47" s="1" t="n">
-        <v>45131</v>
+      <c r="F47" s="2">
+        <v>44999</v>
       </c>
       <c r="G47" t="s">
-        <v>13</v>
-      </c>
-      <c r="H47" s="1" t="n">
-        <v>45176</v>
-      </c>
-    </row>
-    <row r="48">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>151</v>
       </c>
@@ -2685,14 +2791,17 @@
       <c r="E48" t="s">
         <v>153</v>
       </c>
-      <c r="F48" s="1" t="n">
-        <v>45143</v>
+      <c r="F48" s="2">
+        <v>45008</v>
       </c>
       <c r="G48" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="49">
+        <v>13</v>
+      </c>
+      <c r="H48" s="2">
+        <v>45078</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>154</v>
       </c>
@@ -2708,14 +2817,14 @@
       <c r="E49" t="s">
         <v>156</v>
       </c>
-      <c r="F49" s="1" t="n">
-        <v>45148</v>
+      <c r="F49" s="2">
+        <v>45020</v>
       </c>
       <c r="G49" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>157</v>
       </c>
@@ -2731,17 +2840,17 @@
       <c r="E50" t="s">
         <v>159</v>
       </c>
-      <c r="F50" s="1" t="n">
-        <v>45217</v>
+      <c r="F50" s="2">
+        <v>45035</v>
       </c>
       <c r="G50" t="s">
         <v>13</v>
       </c>
-      <c r="H50" s="1" t="n">
-        <v>45247</v>
-      </c>
-    </row>
-    <row r="51">
+      <c r="H50" s="2">
+        <v>45106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>160</v>
       </c>
@@ -2757,17 +2866,17 @@
       <c r="E51" t="s">
         <v>162</v>
       </c>
-      <c r="F51" s="1" t="n">
-        <v>45229</v>
+      <c r="F51" s="2">
+        <v>45041</v>
       </c>
       <c r="G51" t="s">
         <v>13</v>
       </c>
-      <c r="H51" s="1" t="n">
-        <v>45267</v>
-      </c>
-    </row>
-    <row r="52">
+      <c r="H51" s="2">
+        <v>45100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>163</v>
       </c>
@@ -2783,17 +2892,17 @@
       <c r="E52" t="s">
         <v>165</v>
       </c>
-      <c r="F52" s="1" t="n">
-        <v>45233</v>
+      <c r="F52" s="2">
+        <v>45044</v>
       </c>
       <c r="G52" t="s">
         <v>13</v>
       </c>
-      <c r="H52" s="1" t="n">
-        <v>45303</v>
-      </c>
-    </row>
-    <row r="53">
+      <c r="H52" s="2">
+        <v>45091</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>166</v>
       </c>
@@ -2809,17 +2918,17 @@
       <c r="E53" t="s">
         <v>168</v>
       </c>
-      <c r="F53" s="1" t="n">
-        <v>45234</v>
+      <c r="F53" s="2">
+        <v>45044</v>
       </c>
       <c r="G53" t="s">
         <v>13</v>
       </c>
-      <c r="H53" s="1" t="n">
-        <v>45288</v>
-      </c>
-    </row>
-    <row r="54">
+      <c r="H53" s="2">
+        <v>45096</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>169</v>
       </c>
@@ -2835,17 +2944,17 @@
       <c r="E54" t="s">
         <v>171</v>
       </c>
-      <c r="F54" s="1" t="n">
-        <v>45237</v>
+      <c r="F54" s="2">
+        <v>45048</v>
       </c>
       <c r="G54" t="s">
         <v>13</v>
       </c>
-      <c r="H54" s="1" t="n">
-        <v>45289</v>
-      </c>
-    </row>
-    <row r="55">
+      <c r="H54" s="2">
+        <v>45099</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>172</v>
       </c>
@@ -2861,17 +2970,17 @@
       <c r="E55" t="s">
         <v>174</v>
       </c>
-      <c r="F55" s="1" t="n">
-        <v>45250</v>
+      <c r="F55" s="2">
+        <v>45063</v>
       </c>
       <c r="G55" t="s">
         <v>13</v>
       </c>
-      <c r="H55" s="1" t="n">
-        <v>45288</v>
-      </c>
-    </row>
-    <row r="56">
+      <c r="H55" s="2">
+        <v>45140</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>175</v>
       </c>
@@ -2887,17 +2996,14 @@
       <c r="E56" t="s">
         <v>177</v>
       </c>
-      <c r="F56" s="1" t="n">
-        <v>45254</v>
+      <c r="F56" s="2">
+        <v>45113</v>
       </c>
       <c r="G56" t="s">
-        <v>13</v>
-      </c>
-      <c r="H56" s="1" t="n">
-        <v>45311</v>
-      </c>
-    </row>
-    <row r="57">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>178</v>
       </c>
@@ -2913,17 +3019,14 @@
       <c r="E57" t="s">
         <v>180</v>
       </c>
-      <c r="F57" s="1" t="n">
-        <v>45321</v>
+      <c r="F57" s="2">
+        <v>45119</v>
       </c>
       <c r="G57" t="s">
-        <v>13</v>
-      </c>
-      <c r="H57" s="1" t="n">
-        <v>45357</v>
-      </c>
-    </row>
-    <row r="58">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>181</v>
       </c>
@@ -2939,14 +3042,17 @@
       <c r="E58" t="s">
         <v>183</v>
       </c>
-      <c r="F58" s="1" t="n">
-        <v>45345</v>
+      <c r="F58" s="2">
+        <v>45132</v>
       </c>
       <c r="G58" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="59">
+        <v>13</v>
+      </c>
+      <c r="H58" s="2">
+        <v>45180</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>184</v>
       </c>
@@ -2962,17 +3068,17 @@
       <c r="E59" t="s">
         <v>186</v>
       </c>
-      <c r="F59" s="1" t="n">
-        <v>45346</v>
+      <c r="F59" s="2">
+        <v>45133</v>
       </c>
       <c r="G59" t="s">
         <v>13</v>
       </c>
-      <c r="H59" s="1" t="n">
-        <v>45403</v>
-      </c>
-    </row>
-    <row r="60">
+      <c r="H59" s="2">
+        <v>45170</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>187</v>
       </c>
@@ -2988,17 +3094,17 @@
       <c r="E60" t="s">
         <v>189</v>
       </c>
-      <c r="F60" s="1" t="n">
-        <v>45353</v>
+      <c r="F60" s="2">
+        <v>45142</v>
       </c>
       <c r="G60" t="s">
         <v>13</v>
       </c>
-      <c r="H60" s="1" t="n">
-        <v>45419</v>
-      </c>
-    </row>
-    <row r="61">
+      <c r="H60" s="2">
+        <v>45189</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>190</v>
       </c>
@@ -3014,17 +3120,17 @@
       <c r="E61" t="s">
         <v>192</v>
       </c>
-      <c r="F61" s="1" t="n">
-        <v>45361</v>
+      <c r="F61" s="2">
+        <v>45145</v>
       </c>
       <c r="G61" t="s">
-        <v>13</v>
-      </c>
-      <c r="H61" s="1" t="n">
-        <v>45418</v>
-      </c>
-    </row>
-    <row r="62">
+        <v>63</v>
+      </c>
+      <c r="H61" s="2">
+        <v>45196</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>193</v>
       </c>
@@ -3040,17 +3146,17 @@
       <c r="E62" t="s">
         <v>195</v>
       </c>
-      <c r="F62" s="1" t="n">
-        <v>45377</v>
+      <c r="F62" s="2">
+        <v>45187</v>
       </c>
       <c r="G62" t="s">
         <v>13</v>
       </c>
-      <c r="H62" s="1" t="n">
-        <v>45424</v>
-      </c>
-    </row>
-    <row r="63">
+      <c r="H62" s="2">
+        <v>45243</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>196</v>
       </c>
@@ -3066,17 +3172,14 @@
       <c r="E63" t="s">
         <v>198</v>
       </c>
-      <c r="F63" s="1" t="n">
-        <v>45402</v>
+      <c r="F63" s="2">
+        <v>45198</v>
       </c>
       <c r="G63" t="s">
-        <v>13</v>
-      </c>
-      <c r="H63" s="1" t="n">
-        <v>45451</v>
-      </c>
-    </row>
-    <row r="64">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>199</v>
       </c>
@@ -3092,17 +3195,17 @@
       <c r="E64" t="s">
         <v>201</v>
       </c>
-      <c r="F64" s="1" t="n">
-        <v>45404</v>
+      <c r="F64" s="2">
+        <v>45225</v>
       </c>
       <c r="G64" t="s">
         <v>13</v>
       </c>
-      <c r="H64" s="1" t="n">
-        <v>45475</v>
-      </c>
-    </row>
-    <row r="65">
+      <c r="H64" s="2">
+        <v>45252</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>202</v>
       </c>
@@ -3118,17 +3221,17 @@
       <c r="E65" t="s">
         <v>204</v>
       </c>
-      <c r="F65" s="1" t="n">
-        <v>45459</v>
+      <c r="F65" s="2">
+        <v>45226</v>
       </c>
       <c r="G65" t="s">
         <v>13</v>
       </c>
-      <c r="H65" s="1" t="n">
-        <v>45530</v>
-      </c>
-    </row>
-    <row r="66">
+      <c r="H65" s="2">
+        <v>45302</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>205</v>
       </c>
@@ -3144,17 +3247,17 @@
       <c r="E66" t="s">
         <v>207</v>
       </c>
-      <c r="F66" s="1" t="n">
-        <v>45461</v>
+      <c r="F66" s="2">
+        <v>45229</v>
       </c>
       <c r="G66" t="s">
         <v>13</v>
       </c>
-      <c r="H66" s="1" t="n">
-        <v>45526</v>
-      </c>
-    </row>
-    <row r="67">
+      <c r="H66" s="2">
+        <v>45258</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>208</v>
       </c>
@@ -3170,17 +3273,17 @@
       <c r="E67" t="s">
         <v>210</v>
       </c>
-      <c r="F67" s="1" t="n">
-        <v>45506</v>
+      <c r="F67" s="2">
+        <v>45238</v>
       </c>
       <c r="G67" t="s">
         <v>13</v>
       </c>
-      <c r="H67" s="1" t="n">
-        <v>45561</v>
-      </c>
-    </row>
-    <row r="68">
+      <c r="H67" s="2">
+        <v>45302</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>211</v>
       </c>
@@ -3196,17 +3299,14 @@
       <c r="E68" t="s">
         <v>213</v>
       </c>
-      <c r="F68" s="1" t="n">
-        <v>45515</v>
+      <c r="F68" s="2">
+        <v>45240</v>
       </c>
       <c r="G68" t="s">
-        <v>63</v>
-      </c>
-      <c r="H68" s="1" t="n">
-        <v>45556</v>
-      </c>
-    </row>
-    <row r="69">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>214</v>
       </c>
@@ -3222,17 +3322,17 @@
       <c r="E69" t="s">
         <v>216</v>
       </c>
-      <c r="F69" s="1" t="n">
-        <v>45537</v>
+      <c r="F69" s="2">
+        <v>45268</v>
       </c>
       <c r="G69" t="s">
         <v>13</v>
       </c>
-      <c r="H69" s="1" t="n">
-        <v>45596</v>
-      </c>
-    </row>
-    <row r="70">
+      <c r="H69" s="2">
+        <v>45323</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>217</v>
       </c>
@@ -3248,17 +3348,17 @@
       <c r="E70" t="s">
         <v>219</v>
       </c>
-      <c r="F70" s="1" t="n">
-        <v>45574</v>
+      <c r="F70" s="2">
+        <v>45344</v>
       </c>
       <c r="G70" t="s">
         <v>13</v>
       </c>
-      <c r="H70" s="1" t="n">
-        <v>45642</v>
-      </c>
-    </row>
-    <row r="71">
+      <c r="H70" s="2">
+        <v>45371</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>220</v>
       </c>
@@ -3274,14 +3374,17 @@
       <c r="E71" t="s">
         <v>222</v>
       </c>
-      <c r="F71" s="1" t="n">
-        <v>45583</v>
+      <c r="F71" s="2">
+        <v>45349</v>
       </c>
       <c r="G71" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="72">
+        <v>13</v>
+      </c>
+      <c r="H71" s="2">
+        <v>45379</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>223</v>
       </c>
@@ -3297,17 +3400,17 @@
       <c r="E72" t="s">
         <v>225</v>
       </c>
-      <c r="F72" s="1" t="n">
-        <v>45593</v>
+      <c r="F72" s="2">
+        <v>45364</v>
       </c>
       <c r="G72" t="s">
         <v>13</v>
       </c>
-      <c r="H72" s="1" t="n">
-        <v>45632</v>
-      </c>
-    </row>
-    <row r="73">
+      <c r="H72" s="2">
+        <v>45415</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>226</v>
       </c>
@@ -3323,17 +3426,17 @@
       <c r="E73" t="s">
         <v>228</v>
       </c>
-      <c r="F73" s="1" t="n">
-        <v>45628</v>
+      <c r="F73" s="2">
+        <v>45365</v>
       </c>
       <c r="G73" t="s">
         <v>13</v>
       </c>
-      <c r="H73" s="1" t="n">
-        <v>45668</v>
-      </c>
-    </row>
-    <row r="74">
+      <c r="H73" s="2">
+        <v>45422</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>229</v>
       </c>
@@ -3349,17 +3452,14 @@
       <c r="E74" t="s">
         <v>231</v>
       </c>
-      <c r="F74" s="1" t="n">
-        <v>45653</v>
+      <c r="F74" s="2">
+        <v>45371</v>
       </c>
       <c r="G74" t="s">
-        <v>13</v>
-      </c>
-      <c r="H74" s="1" t="n">
-        <v>45707</v>
-      </c>
-    </row>
-    <row r="75">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>232</v>
       </c>
@@ -3375,17 +3475,17 @@
       <c r="E75" t="s">
         <v>234</v>
       </c>
-      <c r="F75" s="1" t="n">
-        <v>45660</v>
+      <c r="F75" s="2">
+        <v>45384</v>
       </c>
       <c r="G75" t="s">
         <v>13</v>
       </c>
-      <c r="H75" s="1" t="n">
-        <v>45686</v>
-      </c>
-    </row>
-    <row r="76">
+      <c r="H75" s="2">
+        <v>45443</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>235</v>
       </c>
@@ -3401,17 +3501,17 @@
       <c r="E76" t="s">
         <v>237</v>
       </c>
-      <c r="F76" s="1" t="n">
-        <v>45668</v>
+      <c r="F76" s="2">
+        <v>45407</v>
       </c>
       <c r="G76" t="s">
         <v>13</v>
       </c>
-      <c r="H76" s="1" t="n">
-        <v>45711</v>
-      </c>
-    </row>
-    <row r="77">
+      <c r="H76" s="2">
+        <v>45434</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>238</v>
       </c>
@@ -3427,17 +3527,17 @@
       <c r="E77" t="s">
         <v>240</v>
       </c>
-      <c r="F77" s="1" t="n">
-        <v>45681</v>
+      <c r="F77" s="2">
+        <v>45425</v>
       </c>
       <c r="G77" t="s">
         <v>13</v>
       </c>
-      <c r="H77" s="1" t="n">
-        <v>45754</v>
-      </c>
-    </row>
-    <row r="78">
+      <c r="H77" s="2">
+        <v>45497</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>241</v>
       </c>
@@ -3453,17 +3553,17 @@
       <c r="E78" t="s">
         <v>243</v>
       </c>
-      <c r="F78" s="1" t="n">
-        <v>45688</v>
+      <c r="F78" s="2">
+        <v>45447</v>
       </c>
       <c r="G78" t="s">
         <v>13</v>
       </c>
-      <c r="H78" s="1" t="n">
-        <v>45738</v>
-      </c>
-    </row>
-    <row r="79">
+      <c r="H78" s="2">
+        <v>45503</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>244</v>
       </c>
@@ -3479,17 +3579,17 @@
       <c r="E79" t="s">
         <v>246</v>
       </c>
-      <c r="F79" s="1" t="n">
-        <v>45693</v>
+      <c r="F79" s="2">
+        <v>45457</v>
       </c>
       <c r="G79" t="s">
         <v>13</v>
       </c>
-      <c r="H79" s="1" t="n">
-        <v>45742</v>
-      </c>
-    </row>
-    <row r="80">
+      <c r="H79" s="2">
+        <v>45504</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>247</v>
       </c>
@@ -3505,17 +3605,14 @@
       <c r="E80" t="s">
         <v>249</v>
       </c>
-      <c r="F80" s="1" t="n">
-        <v>45717</v>
+      <c r="F80" s="2">
+        <v>45492</v>
       </c>
       <c r="G80" t="s">
-        <v>13</v>
-      </c>
-      <c r="H80" s="1" t="n">
-        <v>45789</v>
-      </c>
-    </row>
-    <row r="81">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>250</v>
       </c>
@@ -3531,14 +3628,17 @@
       <c r="E81" t="s">
         <v>252</v>
       </c>
-      <c r="F81" s="1" t="n">
-        <v>45743</v>
+      <c r="F81" s="2">
+        <v>45505</v>
       </c>
       <c r="G81" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="82">
+        <v>13</v>
+      </c>
+      <c r="H81" s="2">
+        <v>45560</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>253</v>
       </c>
@@ -3554,14 +3654,17 @@
       <c r="E82" t="s">
         <v>255</v>
       </c>
-      <c r="F82" s="1" t="n">
-        <v>45753</v>
+      <c r="F82" s="2">
+        <v>45527</v>
       </c>
       <c r="G82" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="83">
+        <v>13</v>
+      </c>
+      <c r="H82" s="2">
+        <v>45572</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>256</v>
       </c>
@@ -3577,17 +3680,17 @@
       <c r="E83" t="s">
         <v>258</v>
       </c>
-      <c r="F83" s="1" t="n">
-        <v>45758</v>
+      <c r="F83" s="2">
+        <v>45534</v>
       </c>
       <c r="G83" t="s">
         <v>13</v>
       </c>
-      <c r="H83" s="1" t="n">
-        <v>45811</v>
-      </c>
-    </row>
-    <row r="84">
+      <c r="H83" s="2">
+        <v>45589</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>259</v>
       </c>
@@ -3603,17 +3706,17 @@
       <c r="E84" t="s">
         <v>261</v>
       </c>
-      <c r="F84" s="1" t="n">
-        <v>45761</v>
+      <c r="F84" s="2">
+        <v>45559</v>
       </c>
       <c r="G84" t="s">
         <v>13</v>
       </c>
-      <c r="H84" s="1" t="n">
-        <v>45807</v>
-      </c>
-    </row>
-    <row r="85">
+      <c r="H84" s="2">
+        <v>45608</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>262</v>
       </c>
@@ -3629,14 +3732,17 @@
       <c r="E85" t="s">
         <v>264</v>
       </c>
-      <c r="F85" s="1" t="n">
-        <v>45802</v>
+      <c r="F85" s="2">
+        <v>45568</v>
       </c>
       <c r="G85" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="86">
+        <v>13</v>
+      </c>
+      <c r="H85" s="2">
+        <v>45631</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>265</v>
       </c>
@@ -3652,17 +3758,17 @@
       <c r="E86" t="s">
         <v>267</v>
       </c>
-      <c r="F86" s="1" t="n">
-        <v>45804</v>
+      <c r="F86" s="2">
+        <v>45576</v>
       </c>
       <c r="G86" t="s">
         <v>13</v>
       </c>
-      <c r="H86" s="1" t="n">
-        <v>45861</v>
-      </c>
-    </row>
-    <row r="87">
+      <c r="H86" s="2">
+        <v>45603</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>268</v>
       </c>
@@ -3678,17 +3784,17 @@
       <c r="E87" t="s">
         <v>270</v>
       </c>
-      <c r="F87" s="1" t="n">
-        <v>45805</v>
+      <c r="F87" s="2">
+        <v>45583</v>
       </c>
       <c r="G87" t="s">
-        <v>63</v>
-      </c>
-      <c r="H87" s="1" t="n">
-        <v>45850</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>13</v>
+      </c>
+      <c r="H87" s="2">
+        <v>45618</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>271</v>
       </c>
@@ -3704,17 +3810,17 @@
       <c r="E88" t="s">
         <v>273</v>
       </c>
-      <c r="F88" s="1" t="n">
-        <v>45808</v>
+      <c r="F88" s="2">
+        <v>45601</v>
       </c>
       <c r="G88" t="s">
         <v>13</v>
       </c>
-      <c r="H88" s="1" t="n">
-        <v>45882</v>
-      </c>
-    </row>
-    <row r="89">
+      <c r="H88" s="2">
+        <v>45650</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>274</v>
       </c>
@@ -3730,17 +3836,17 @@
       <c r="E89" t="s">
         <v>276</v>
       </c>
-      <c r="F89" s="1" t="n">
-        <v>45879</v>
+      <c r="F89" s="2">
+        <v>45618</v>
       </c>
       <c r="G89" t="s">
         <v>13</v>
       </c>
-      <c r="H89" s="1" t="n">
-        <v>45909</v>
-      </c>
-    </row>
-    <row r="90">
+      <c r="H89" s="2">
+        <v>45649</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>277</v>
       </c>
@@ -3756,17 +3862,17 @@
       <c r="E90" t="s">
         <v>279</v>
       </c>
-      <c r="F90" s="1" t="n">
-        <v>45917</v>
+      <c r="F90" s="2">
+        <v>45630</v>
       </c>
       <c r="G90" t="s">
         <v>13</v>
       </c>
-      <c r="H90" s="1" t="n">
-        <v>45943</v>
-      </c>
-    </row>
-    <row r="91">
+      <c r="H90" s="2">
+        <v>45687</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>280</v>
       </c>
@@ -3782,17 +3888,14 @@
       <c r="E91" t="s">
         <v>282</v>
       </c>
-      <c r="F91" s="1" t="n">
-        <v>45923</v>
+      <c r="F91" s="2">
+        <v>45646</v>
       </c>
       <c r="G91" t="s">
-        <v>13</v>
-      </c>
-      <c r="H91" s="1" t="n">
-        <v>45969</v>
-      </c>
-    </row>
-    <row r="92">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>283</v>
       </c>
@@ -3808,17 +3911,17 @@
       <c r="E92" t="s">
         <v>285</v>
       </c>
-      <c r="F92" s="1" t="n">
-        <v>45941</v>
+      <c r="F92" s="2">
+        <v>45665</v>
       </c>
       <c r="G92" t="s">
         <v>13</v>
       </c>
-      <c r="H92" s="1" t="n">
-        <v>45986</v>
-      </c>
-    </row>
-    <row r="93">
+      <c r="H92" s="2">
+        <v>45702</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>286</v>
       </c>
@@ -3834,14 +3937,14 @@
       <c r="E93" t="s">
         <v>288</v>
       </c>
-      <c r="F93" s="1" t="n">
-        <v>45948</v>
+      <c r="F93" s="2">
+        <v>45672</v>
       </c>
       <c r="G93" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>289</v>
       </c>
@@ -3857,14 +3960,17 @@
       <c r="E94" t="s">
         <v>291</v>
       </c>
-      <c r="F94" s="1" t="n">
-        <v>45952</v>
+      <c r="F94" s="2">
+        <v>45674</v>
       </c>
       <c r="G94" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="95">
+        <v>13</v>
+      </c>
+      <c r="H94" s="2">
+        <v>45701</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>292</v>
       </c>
@@ -3880,17 +3986,17 @@
       <c r="E95" t="s">
         <v>294</v>
       </c>
-      <c r="F95" s="1" t="n">
-        <v>45957</v>
+      <c r="F95" s="2">
+        <v>45678</v>
       </c>
       <c r="G95" t="s">
         <v>13</v>
       </c>
-      <c r="H95" s="1" t="n">
-        <v>46008</v>
-      </c>
-    </row>
-    <row r="96">
+      <c r="H95" s="2">
+        <v>45720</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>295</v>
       </c>
@@ -3906,17 +4012,17 @@
       <c r="E96" t="s">
         <v>297</v>
       </c>
-      <c r="F96" s="1" t="n">
-        <v>45973</v>
+      <c r="F96" s="2">
+        <v>45686</v>
       </c>
       <c r="G96" t="s">
         <v>13</v>
       </c>
-      <c r="H96" s="1" t="n">
-        <v>46025</v>
-      </c>
-    </row>
-    <row r="97">
+      <c r="H96" s="2">
+        <v>45737</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>298</v>
       </c>
@@ -3932,14 +4038,17 @@
       <c r="E97" t="s">
         <v>300</v>
       </c>
-      <c r="F97" s="1" t="n">
-        <v>45974</v>
+      <c r="F97" s="2">
+        <v>45688</v>
       </c>
       <c r="G97" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="98">
+        <v>13</v>
+      </c>
+      <c r="H97" s="2">
+        <v>45757</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>301</v>
       </c>
@@ -3955,17 +4064,17 @@
       <c r="E98" t="s">
         <v>303</v>
       </c>
-      <c r="F98" s="1" t="n">
-        <v>45980</v>
+      <c r="F98" s="2">
+        <v>45693</v>
       </c>
       <c r="G98" t="s">
         <v>13</v>
       </c>
-      <c r="H98" s="1" t="n">
-        <v>46053</v>
-      </c>
-    </row>
-    <row r="99">
+      <c r="H98" s="2">
+        <v>45769</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>304</v>
       </c>
@@ -3981,14 +4090,17 @@
       <c r="E99" t="s">
         <v>306</v>
       </c>
-      <c r="F99" s="1" t="n">
-        <v>45999</v>
+      <c r="F99" s="2">
+        <v>45706</v>
       </c>
       <c r="G99" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100">
+        <v>13</v>
+      </c>
+      <c r="H99" s="2">
+        <v>45754</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>307</v>
       </c>
@@ -4004,17 +4116,14 @@
       <c r="E100" t="s">
         <v>309</v>
       </c>
-      <c r="F100" s="1" t="n">
-        <v>46012</v>
+      <c r="F100" s="2">
+        <v>45715</v>
       </c>
       <c r="G100" t="s">
-        <v>13</v>
-      </c>
-      <c r="H100" s="1" t="n">
-        <v>46048</v>
-      </c>
-    </row>
-    <row r="101">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>310</v>
       </c>
@@ -4030,17 +4139,17 @@
       <c r="E101" t="s">
         <v>312</v>
       </c>
-      <c r="F101" s="1" t="n">
-        <v>46022</v>
+      <c r="F101" s="2">
+        <v>45799</v>
       </c>
       <c r="G101" t="s">
         <v>13</v>
       </c>
-      <c r="H101" s="1" t="n">
-        <v>46083</v>
-      </c>
-    </row>
-    <row r="102">
+      <c r="H101" s="2">
+        <v>45875</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>313</v>
       </c>
@@ -4056,17 +4165,17 @@
       <c r="E102" t="s">
         <v>315</v>
       </c>
-      <c r="F102" s="1" t="n">
-        <v>46050</v>
+      <c r="F102" s="2">
+        <v>45800</v>
       </c>
       <c r="G102" t="s">
         <v>13</v>
       </c>
-      <c r="H102" s="1" t="n">
-        <v>46092</v>
-      </c>
-    </row>
-    <row r="103">
+      <c r="H102" s="2">
+        <v>45869</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>316</v>
       </c>
@@ -4082,14 +4191,17 @@
       <c r="E103" t="s">
         <v>318</v>
       </c>
-      <c r="F103" s="1" t="n">
-        <v>46057</v>
+      <c r="F103" s="2">
+        <v>45812</v>
       </c>
       <c r="G103" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="104">
+        <v>63</v>
+      </c>
+      <c r="H103" s="2">
+        <v>45853</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>319</v>
       </c>
@@ -4105,17 +4217,17 @@
       <c r="E104" t="s">
         <v>321</v>
       </c>
-      <c r="F104" s="1" t="n">
-        <v>46062</v>
+      <c r="F104" s="2">
+        <v>45813</v>
       </c>
       <c r="G104" t="s">
         <v>13</v>
       </c>
-      <c r="H104" s="1" t="n">
-        <v>46105</v>
-      </c>
-    </row>
-    <row r="105">
+      <c r="H104" s="2">
+        <v>45882</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>322</v>
       </c>
@@ -4131,17 +4243,14 @@
       <c r="E105" t="s">
         <v>324</v>
       </c>
-      <c r="F105" s="1" t="n">
-        <v>46063</v>
+      <c r="F105" s="2">
+        <v>45855</v>
       </c>
       <c r="G105" t="s">
-        <v>13</v>
-      </c>
-      <c r="H105" s="1" t="n">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="106">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>325</v>
       </c>
@@ -4157,17 +4266,14 @@
       <c r="E106" t="s">
         <v>327</v>
       </c>
-      <c r="F106" s="1" t="n">
-        <v>46094</v>
+      <c r="F106" s="2">
+        <v>45870</v>
       </c>
       <c r="G106" t="s">
-        <v>13</v>
-      </c>
-      <c r="H106" s="1" t="n">
-        <v>46139</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>328</v>
       </c>
@@ -4183,17 +4289,14 @@
       <c r="E107" t="s">
         <v>330</v>
       </c>
-      <c r="F107" s="1" t="n">
-        <v>46135</v>
+      <c r="F107" s="2">
+        <v>45883</v>
       </c>
       <c r="G107" t="s">
-        <v>13</v>
-      </c>
-      <c r="H107" s="1" t="n">
-        <v>46208</v>
-      </c>
-    </row>
-    <row r="108">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>331</v>
       </c>
@@ -4209,17 +4312,17 @@
       <c r="E108" t="s">
         <v>333</v>
       </c>
-      <c r="F108" s="1" t="n">
-        <v>46143</v>
+      <c r="F108" s="2">
+        <v>45891</v>
       </c>
       <c r="G108" t="s">
-        <v>13</v>
-      </c>
-      <c r="H108" s="1" t="n">
-        <v>46186</v>
-      </c>
-    </row>
-    <row r="109">
+        <v>63</v>
+      </c>
+      <c r="H108" s="2">
+        <v>45966</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>334</v>
       </c>
@@ -4235,17 +4338,17 @@
       <c r="E109" t="s">
         <v>336</v>
       </c>
-      <c r="F109" s="1" t="n">
-        <v>46178</v>
+      <c r="F109" s="2">
+        <v>45919</v>
       </c>
       <c r="G109" t="s">
         <v>13</v>
       </c>
-      <c r="H109" s="1" t="n">
-        <v>46236</v>
-      </c>
-    </row>
-    <row r="110">
+      <c r="H109" s="2">
+        <v>45988</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>337</v>
       </c>
@@ -4261,109 +4364,503 @@
       <c r="E110" t="s">
         <v>339</v>
       </c>
-      <c r="F110" s="1" t="n">
-        <v>46252</v>
+      <c r="F110" s="2">
+        <v>45937</v>
       </c>
       <c r="G110" t="s">
+        <v>13</v>
+      </c>
+      <c r="H110" s="2">
+        <v>45993</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
+      <c r="B111" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" t="s">
         <v>341</v>
       </c>
-      <c r="B111" t="s">
-        <v>9</v>
-      </c>
-      <c r="C111" t="s">
+      <c r="D111" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" t="s">
         <v>342</v>
       </c>
-      <c r="D111" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="F111" s="2">
+        <v>45944</v>
+      </c>
+      <c r="G111" t="s">
+        <v>13</v>
+      </c>
+      <c r="H111" s="2">
+        <v>45979</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
         <v>343</v>
       </c>
-      <c r="F111" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="G111" t="s">
-        <v>13</v>
-      </c>
-      <c r="H111" s="1" t="n">
-        <v>46294</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
+      <c r="B112" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112" t="s">
         <v>344</v>
       </c>
-      <c r="B112" t="s">
-        <v>9</v>
-      </c>
-      <c r="C112" t="s">
+      <c r="D112" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" t="s">
         <v>345</v>
       </c>
-      <c r="D112" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" t="s">
+      <c r="F112" s="2">
+        <v>45966</v>
+      </c>
+      <c r="G112" t="s">
+        <v>13</v>
+      </c>
+      <c r="H112" s="2">
+        <v>46038</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
         <v>346</v>
       </c>
-      <c r="F112" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="G112" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
+      <c r="B113" t="s">
+        <v>9</v>
+      </c>
+      <c r="C113" t="s">
         <v>347</v>
       </c>
-      <c r="B113" t="s">
-        <v>9</v>
-      </c>
-      <c r="C113" t="s">
+      <c r="D113" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" t="s">
         <v>348</v>
       </c>
-      <c r="D113" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" t="s">
+      <c r="F113" s="2">
+        <v>45971</v>
+      </c>
+      <c r="G113" t="s">
+        <v>13</v>
+      </c>
+      <c r="H113" s="2">
+        <v>46020</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
         <v>349</v>
       </c>
-      <c r="F113" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="G113" t="s">
+      <c r="B114" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114" t="s">
+        <v>350</v>
+      </c>
+      <c r="D114" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" t="s">
+        <v>351</v>
+      </c>
+      <c r="F114" s="2">
+        <v>45972</v>
+      </c>
+      <c r="G114" t="s">
+        <v>13</v>
+      </c>
+      <c r="H114" s="2">
+        <v>46010</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>352</v>
+      </c>
+      <c r="B115" t="s">
+        <v>9</v>
+      </c>
+      <c r="C115" t="s">
+        <v>353</v>
+      </c>
+      <c r="D115" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" t="s">
+        <v>354</v>
+      </c>
+      <c r="F115" s="2">
+        <v>45994</v>
+      </c>
+      <c r="G115" t="s">
+        <v>13</v>
+      </c>
+      <c r="H115" s="2">
+        <v>46029</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>355</v>
+      </c>
+      <c r="B116" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116" t="s">
+        <v>356</v>
+      </c>
+      <c r="D116" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" t="s">
+        <v>357</v>
+      </c>
+      <c r="F116" s="2">
+        <v>46055</v>
+      </c>
+      <c r="G116" t="s">
+        <v>13</v>
+      </c>
+      <c r="H116" s="2">
+        <v>46106</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>358</v>
+      </c>
+      <c r="B117" t="s">
+        <v>9</v>
+      </c>
+      <c r="C117" t="s">
+        <v>359</v>
+      </c>
+      <c r="D117" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" t="s">
+        <v>360</v>
+      </c>
+      <c r="F117" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G117" t="s">
+        <v>13</v>
+      </c>
+      <c r="H117" s="2">
+        <v>46127</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>361</v>
+      </c>
+      <c r="B118" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" t="s">
+        <v>362</v>
+      </c>
+      <c r="D118" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" t="s">
+        <v>363</v>
+      </c>
+      <c r="F118" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G118" t="s">
+        <v>13</v>
+      </c>
+      <c r="H118" s="2">
+        <v>46097</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>364</v>
+      </c>
+      <c r="B119" t="s">
+        <v>9</v>
+      </c>
+      <c r="C119" t="s">
+        <v>365</v>
+      </c>
+      <c r="D119" t="s">
+        <v>11</v>
+      </c>
+      <c r="E119" t="s">
+        <v>366</v>
+      </c>
+      <c r="F119" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G119" t="s">
+        <v>13</v>
+      </c>
+      <c r="H119" s="2">
+        <v>46104</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>367</v>
+      </c>
+      <c r="B120" t="s">
+        <v>9</v>
+      </c>
+      <c r="C120" t="s">
+        <v>368</v>
+      </c>
+      <c r="D120" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" t="s">
+        <v>369</v>
+      </c>
+      <c r="F120" s="2">
+        <v>46076</v>
+      </c>
+      <c r="G120" t="s">
+        <v>13</v>
+      </c>
+      <c r="H120" s="2">
+        <v>46118</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>370</v>
+      </c>
+      <c r="B121" t="s">
+        <v>9</v>
+      </c>
+      <c r="C121" t="s">
+        <v>371</v>
+      </c>
+      <c r="D121" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" t="s">
+        <v>372</v>
+      </c>
+      <c r="F121" s="2">
+        <v>46094</v>
+      </c>
+      <c r="G121" t="s">
+        <v>13</v>
+      </c>
+      <c r="H121" s="2">
+        <v>46122</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>373</v>
+      </c>
+      <c r="B122" t="s">
+        <v>9</v>
+      </c>
+      <c r="C122" t="s">
+        <v>374</v>
+      </c>
+      <c r="D122" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" t="s">
+        <v>375</v>
+      </c>
+      <c r="F122" s="2">
+        <v>46113</v>
+      </c>
+      <c r="G122" t="s">
+        <v>13</v>
+      </c>
+      <c r="H122" s="2">
+        <v>46189</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>376</v>
+      </c>
+      <c r="B123" t="s">
+        <v>9</v>
+      </c>
+      <c r="C123" t="s">
+        <v>377</v>
+      </c>
+      <c r="D123" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" t="s">
+        <v>378</v>
+      </c>
+      <c r="F123" s="2">
+        <v>46140</v>
+      </c>
+      <c r="G123" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>350</v>
-      </c>
-      <c r="B114" t="s">
-        <v>9</v>
-      </c>
-      <c r="C114" t="s">
-        <v>351</v>
-      </c>
-      <c r="D114" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" t="s">
-        <v>352</v>
-      </c>
-      <c r="F114" s="1" t="n">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>379</v>
+      </c>
+      <c r="B124" t="s">
+        <v>9</v>
+      </c>
+      <c r="C124" t="s">
+        <v>380</v>
+      </c>
+      <c r="D124" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" t="s">
+        <v>381</v>
+      </c>
+      <c r="F124" s="2">
+        <v>46155</v>
+      </c>
+      <c r="G124" t="s">
+        <v>13</v>
+      </c>
+      <c r="H124" s="2">
+        <v>46184</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>382</v>
+      </c>
+      <c r="B125" t="s">
+        <v>9</v>
+      </c>
+      <c r="C125" t="s">
+        <v>383</v>
+      </c>
+      <c r="D125" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" t="s">
+        <v>384</v>
+      </c>
+      <c r="F125" s="2">
+        <v>46161</v>
+      </c>
+      <c r="G125" t="s">
+        <v>13</v>
+      </c>
+      <c r="H125" s="2">
+        <v>46195</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>385</v>
+      </c>
+      <c r="B126" t="s">
+        <v>9</v>
+      </c>
+      <c r="C126" t="s">
+        <v>386</v>
+      </c>
+      <c r="D126" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" t="s">
+        <v>387</v>
+      </c>
+      <c r="F126" s="2">
+        <v>46254</v>
+      </c>
+      <c r="G126" t="s">
+        <v>13</v>
+      </c>
+      <c r="H126" s="2">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>388</v>
+      </c>
+      <c r="B127" t="s">
+        <v>9</v>
+      </c>
+      <c r="C127" t="s">
+        <v>389</v>
+      </c>
+      <c r="D127" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" t="s">
+        <v>390</v>
+      </c>
+      <c r="F127" s="2">
+        <v>46255</v>
+      </c>
+      <c r="G127" t="s">
+        <v>13</v>
+      </c>
+      <c r="H127" s="2">
+        <v>46282</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>391</v>
+      </c>
+      <c r="B128" t="s">
+        <v>9</v>
+      </c>
+      <c r="C128" t="s">
+        <v>392</v>
+      </c>
+      <c r="D128" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" t="s">
+        <v>393</v>
+      </c>
+      <c r="F128" s="2">
+        <v>46281</v>
+      </c>
+      <c r="G128" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>395</v>
+      </c>
+      <c r="B129" t="s">
+        <v>9</v>
+      </c>
+      <c r="C129" t="s">
+        <v>396</v>
+      </c>
+      <c r="D129" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" t="s">
+        <v>397</v>
+      </c>
+      <c r="F129" s="2">
         <v>46289</v>
       </c>
-      <c r="G114" t="s">
-        <v>26</v>
+      <c r="G129" t="s">
+        <v>394</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:H129"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/task132/target/veldtek_rma_log_vpr340_psu.xlsx
+++ b/task132/target/veldtek_rma_log_vpr340_psu.xlsx
@@ -53,7 +53,7 @@
     <t>VPR340-PSU-02</t>
   </si>
   <si>
-    <t>PS02-92-21039</t>
+    <t>PS02-92-02261</t>
   </si>
   <si>
     <t>Tarrock Hydro</t>
@@ -68,7 +68,7 @@
     <t>RMA-12031</t>
   </si>
   <si>
-    <t>PS02-92-21026</t>
+    <t>PS02-92-02225</t>
   </si>
   <si>
     <t>469358</t>
@@ -80,7 +80,7 @@
     <t>RMA-12033</t>
   </si>
   <si>
-    <t>PS02-92-21037</t>
+    <t>PS02-92-02255</t>
   </si>
   <si>
     <t>SB-15-02 / 469358</t>
@@ -89,7 +89,7 @@
     <t>RMA-12034</t>
   </si>
   <si>
-    <t>PS02-92-21022</t>
+    <t>PS02-92-02213</t>
   </si>
   <si>
     <t>SB-15-02 exchange, credit issued</t>
@@ -98,7 +98,7 @@
     <t>RMA-12109</t>
   </si>
   <si>
-    <t>PS02-93-21118</t>
+    <t>PS02-93-02472</t>
   </si>
   <si>
     <t>469895</t>
@@ -107,19 +107,19 @@
     <t>RMA-12110</t>
   </si>
   <si>
-    <t>PS02-93-21117</t>
+    <t>PS02-93-02470</t>
   </si>
   <si>
     <t>RMA-12111</t>
   </si>
   <si>
-    <t>PS02-93-21109</t>
+    <t>PS02-93-02449</t>
   </si>
   <si>
     <t>RMA-12124</t>
   </si>
   <si>
-    <t>PS02-12-25374</t>
+    <t>PS02-12-13770</t>
   </si>
   <si>
     <t>470091</t>
@@ -134,7 +134,7 @@
     <t>RMA-12145</t>
   </si>
   <si>
-    <t>PS02-97-21551</t>
+    <t>PS02-97-03615</t>
   </si>
   <si>
     <t>470313</t>
@@ -143,13 +143,13 @@
     <t>RMA-12148</t>
   </si>
   <si>
-    <t>PS02-97-21578</t>
+    <t>PS02-97-03686</t>
   </si>
   <si>
     <t>RMA-12182</t>
   </si>
   <si>
-    <t>PS02-94-21224</t>
+    <t>PS02-94-02757</t>
   </si>
   <si>
     <t>470410</t>
@@ -158,7 +158,7 @@
     <t>RMA-12183</t>
   </si>
   <si>
-    <t>PS02-94-21166</t>
+    <t>PS02-94-02597</t>
   </si>
   <si>
     <t>SB-15-02 / 470410</t>
@@ -167,13 +167,13 @@
     <t>RMA-12186</t>
   </si>
   <si>
-    <t>PS02-94-21152</t>
+    <t>PS02-94-02562</t>
   </si>
   <si>
     <t>RMA-12189</t>
   </si>
   <si>
-    <t>PS02-97-21583</t>
+    <t>PS02-97-03700</t>
   </si>
   <si>
     <t>SB-15-02 / 470168</t>
@@ -182,7 +182,7 @@
     <t>RMA-12201</t>
   </si>
   <si>
-    <t>PS02-10-24729</t>
+    <t>PS02-10-12046</t>
   </si>
   <si>
     <t>470917</t>
@@ -194,7 +194,7 @@
     <t>RMA-12231</t>
   </si>
   <si>
-    <t>PS02-95-21270</t>
+    <t>PS02-95-02878</t>
   </si>
   <si>
     <t>SB-15-02 / 470945</t>
@@ -203,7 +203,7 @@
     <t>RMA-12246</t>
   </si>
   <si>
-    <t>PS02-95-21261</t>
+    <t>PS02-95-02856</t>
   </si>
   <si>
     <t>470832</t>
@@ -212,7 +212,7 @@
     <t>RMA-12247</t>
   </si>
   <si>
-    <t>PS02-97-21550</t>
+    <t>PS02-97-03614</t>
   </si>
   <si>
     <t>SB-15-02 / 470779</t>
@@ -221,7 +221,7 @@
     <t>RMA-12248</t>
   </si>
   <si>
-    <t>PS02-96-21297</t>
+    <t>PS02-96-02950</t>
   </si>
   <si>
     <t>470779</t>
@@ -230,49 +230,49 @@
     <t>RMA-12251</t>
   </si>
   <si>
-    <t>PS02-95-21247</t>
+    <t>PS02-95-02818</t>
   </si>
   <si>
     <t>RMA-12252</t>
   </si>
   <si>
-    <t>PS02-95-21254</t>
+    <t>PS02-95-02836</t>
   </si>
   <si>
     <t>RMA-12253</t>
   </si>
   <si>
-    <t>PS02-95-21269</t>
+    <t>PS02-95-02877</t>
   </si>
   <si>
     <t>RMA-12254</t>
   </si>
   <si>
-    <t>PS02-97-21530</t>
+    <t>PS02-97-03560</t>
   </si>
   <si>
     <t>RMA-12255</t>
   </si>
   <si>
-    <t>PS02-97-21541</t>
+    <t>PS02-97-03590</t>
   </si>
   <si>
     <t>RMA-12256</t>
   </si>
   <si>
-    <t>PS02-97-21584</t>
+    <t>PS02-97-03701</t>
   </si>
   <si>
     <t>RMA-12257</t>
   </si>
   <si>
-    <t>PS02-97-21562</t>
+    <t>PS02-97-03643</t>
   </si>
   <si>
     <t>RMA-12290</t>
   </si>
   <si>
-    <t>PS02-96-21380</t>
+    <t>PS02-96-03166</t>
   </si>
   <si>
     <t>471395</t>
@@ -281,7 +281,7 @@
     <t>RMA-12307</t>
   </si>
   <si>
-    <t>PS02-95-21273</t>
+    <t>PS02-95-02887</t>
   </si>
   <si>
     <t>SB-15-02 / 471535</t>
@@ -290,13 +290,13 @@
     <t>RMA-12310</t>
   </si>
   <si>
-    <t>PS02-96-21276</t>
+    <t>PS02-96-02896</t>
   </si>
   <si>
     <t>RMA-12311</t>
   </si>
   <si>
-    <t>PS02-94-21171</t>
+    <t>PS02-94-02611</t>
   </si>
   <si>
     <t>471535</t>
@@ -305,73 +305,73 @@
     <t>RMA-12312</t>
   </si>
   <si>
-    <t>PS02-95-21239</t>
+    <t>PS02-95-02795</t>
   </si>
   <si>
     <t>RMA-12313</t>
   </si>
   <si>
-    <t>PS02-92-21056</t>
+    <t>PS02-92-02303</t>
   </si>
   <si>
     <t>RMA-12314</t>
   </si>
   <si>
-    <t>PS02-97-21413</t>
+    <t>PS02-97-03253</t>
   </si>
   <si>
     <t>RMA-12315</t>
   </si>
   <si>
-    <t>PS02-94-21184</t>
+    <t>PS02-94-02646</t>
   </si>
   <si>
     <t>RMA-12316</t>
   </si>
   <si>
-    <t>PS02-95-21242</t>
+    <t>PS02-95-02804</t>
   </si>
   <si>
     <t>RMA-12317</t>
   </si>
   <si>
-    <t>PS02-94-21220</t>
+    <t>PS02-94-02747</t>
   </si>
   <si>
     <t>RMA-12318</t>
   </si>
   <si>
-    <t>PS02-94-21196</t>
+    <t>PS02-94-02679</t>
   </si>
   <si>
     <t>RMA-12319</t>
   </si>
   <si>
-    <t>PS02-94-21214</t>
+    <t>PS02-94-02730</t>
   </si>
   <si>
     <t>RMA-12320</t>
   </si>
   <si>
-    <t>PS02-95-21244</t>
+    <t>PS02-95-02809</t>
   </si>
   <si>
     <t>RMA-12321</t>
   </si>
   <si>
-    <t>PS02-94-21207</t>
+    <t>PS02-94-02710</t>
   </si>
   <si>
     <t>RMA-12322</t>
   </si>
   <si>
-    <t>PS02-96-21312</t>
+    <t>PS02-96-02988</t>
   </si>
   <si>
     <t>RMA-12323</t>
   </si>
   <si>
-    <t>PS02-97-21465</t>
+    <t>PS02-97-03392</t>
   </si>
   <si>
     <t>471633</t>
@@ -380,7 +380,7 @@
     <t>RMA-12324</t>
   </si>
   <si>
-    <t>PS02-96-21322</t>
+    <t>PS02-96-03009</t>
   </si>
   <si>
     <t>SB-15-02 / 471633</t>
@@ -389,97 +389,97 @@
     <t>RMA-12325</t>
   </si>
   <si>
-    <t>PS02-97-21429</t>
+    <t>PS02-97-03298</t>
   </si>
   <si>
     <t>RMA-12326</t>
   </si>
   <si>
-    <t>PS02-97-21489</t>
+    <t>PS02-97-03453</t>
   </si>
   <si>
     <t>RMA-12327</t>
   </si>
   <si>
-    <t>PS02-96-21289</t>
+    <t>PS02-96-02929</t>
   </si>
   <si>
     <t>RMA-12328</t>
   </si>
   <si>
-    <t>PS02-96-21345</t>
+    <t>PS02-96-03071</t>
   </si>
   <si>
     <t>RMA-12329</t>
   </si>
   <si>
-    <t>PS02-97-21486</t>
+    <t>PS02-97-03446</t>
   </si>
   <si>
     <t>RMA-12330</t>
   </si>
   <si>
-    <t>PS02-97-21435</t>
+    <t>PS02-97-03313</t>
   </si>
   <si>
     <t>RMA-12331</t>
   </si>
   <si>
-    <t>PS02-96-21375</t>
+    <t>PS02-96-03152</t>
   </si>
   <si>
     <t>RMA-12332</t>
   </si>
   <si>
-    <t>PS02-96-21282</t>
+    <t>PS02-96-02911</t>
   </si>
   <si>
     <t>RMA-12333</t>
   </si>
   <si>
-    <t>PS02-97-21441</t>
+    <t>PS02-97-03329</t>
   </si>
   <si>
     <t>RMA-12334</t>
   </si>
   <si>
-    <t>PS02-97-21411</t>
+    <t>PS02-97-03247</t>
   </si>
   <si>
     <t>RMA-12335</t>
   </si>
   <si>
-    <t>PS02-96-21355</t>
+    <t>PS02-96-03099</t>
   </si>
   <si>
     <t>RMA-12336</t>
   </si>
   <si>
-    <t>PS02-97-21499</t>
+    <t>PS02-97-03479</t>
   </si>
   <si>
     <t>RMA-12337</t>
   </si>
   <si>
-    <t>PS02-96-21341</t>
+    <t>PS02-96-03061</t>
   </si>
   <si>
     <t>RMA-12338</t>
   </si>
   <si>
-    <t>PS02-96-21325</t>
+    <t>PS02-96-03016</t>
   </si>
   <si>
     <t>RMA-12339</t>
   </si>
   <si>
-    <t>PS02-97-21495</t>
+    <t>PS02-97-03469</t>
   </si>
   <si>
     <t>RMA-12340</t>
   </si>
   <si>
-    <t>PS02-92-21035</t>
+    <t>PS02-92-02249</t>
   </si>
   <si>
     <t>471467</t>
@@ -488,19 +488,19 @@
     <t>RMA-12341</t>
   </si>
   <si>
-    <t>PS02-94-21137</t>
+    <t>PS02-94-02522</t>
   </si>
   <si>
     <t>RMA-12342</t>
   </si>
   <si>
-    <t>PS02-92-21027</t>
+    <t>PS02-92-02227</t>
   </si>
   <si>
     <t>RMA-12343</t>
   </si>
   <si>
-    <t>PS02-90-21011</t>
+    <t>PS02-90-02183</t>
   </si>
   <si>
     <t>SB-15-02 / 471467</t>
@@ -509,13 +509,13 @@
     <t>RMA-12344</t>
   </si>
   <si>
-    <t>PS02-97-21483</t>
+    <t>PS02-97-03439</t>
   </si>
   <si>
     <t>RMA-12351</t>
   </si>
   <si>
-    <t>PS02-92-21062</t>
+    <t>PS02-92-02320</t>
   </si>
   <si>
     <t>471898</t>
@@ -524,13 +524,13 @@
     <t>RMA-12352</t>
   </si>
   <si>
-    <t>PS02-92-21052</t>
+    <t>PS02-92-02292</t>
   </si>
   <si>
     <t>RMA-12356</t>
   </si>
   <si>
-    <t>PS02-92-21071</t>
+    <t>PS02-92-02345</t>
   </si>
   <si>
     <t>SB-15-02 / 471898</t>
@@ -539,13 +539,13 @@
     <t>RMA-12357</t>
   </si>
   <si>
-    <t>PS02-93-21084</t>
+    <t>PS02-93-02380</t>
   </si>
   <si>
     <t>RMA-12358</t>
   </si>
   <si>
-    <t>PS02-05-23159</t>
+    <t>PS02-05-07894</t>
   </si>
   <si>
     <t>471793</t>
@@ -557,31 +557,31 @@
     <t>RMA-12359</t>
   </si>
   <si>
-    <t>PS02-93-21089</t>
+    <t>PS02-93-02394</t>
   </si>
   <si>
     <t>RMA-12360</t>
   </si>
   <si>
-    <t>PS02-93-21086</t>
+    <t>PS02-93-02385</t>
   </si>
   <si>
     <t>RMA-12361</t>
   </si>
   <si>
-    <t>PS02-97-21503</t>
+    <t>PS02-97-03489</t>
   </si>
   <si>
     <t>RMA-12368</t>
   </si>
   <si>
-    <t>PS02-96-21298</t>
+    <t>PS02-96-02953</t>
   </si>
   <si>
     <t>RMA-12369</t>
   </si>
   <si>
-    <t>PS02-97-21501</t>
+    <t>PS02-97-03484</t>
   </si>
   <si>
     <t>471751</t>
@@ -590,13 +590,13 @@
     <t>RMA-12370</t>
   </si>
   <si>
-    <t>PS02-96-21309</t>
+    <t>PS02-96-02981</t>
   </si>
   <si>
     <t>RMA-12386</t>
   </si>
   <si>
-    <t>PS02-97-21555</t>
+    <t>PS02-97-03624</t>
   </si>
   <si>
     <t>471794</t>
@@ -605,7 +605,7 @@
     <t>RMA-12445</t>
   </si>
   <si>
-    <t>PS02-97-21519</t>
+    <t>PS02-97-03531</t>
   </si>
   <si>
     <t>472483</t>
@@ -614,7 +614,7 @@
     <t>RMA-12446</t>
   </si>
   <si>
-    <t>PS02-97-21526</t>
+    <t>PS02-97-03550</t>
   </si>
   <si>
     <t>SB-15-02 / 472483</t>
@@ -623,7 +623,7 @@
     <t>RMA-12483</t>
   </si>
   <si>
-    <t>PS02-97-21412</t>
+    <t>PS02-97-03250</t>
   </si>
   <si>
     <t>472383</t>
@@ -632,7 +632,7 @@
     <t>RMA-12485</t>
   </si>
   <si>
-    <t>PS02-96-21381</t>
+    <t>PS02-96-03168</t>
   </si>
   <si>
     <t>SB-15-02 / 472383</t>
@@ -641,79 +641,79 @@
     <t>RMA-12486</t>
   </si>
   <si>
-    <t>PS02-97-21421</t>
+    <t>PS02-97-03275</t>
   </si>
   <si>
     <t>RMA-12487</t>
   </si>
   <si>
-    <t>PS02-97-21461</t>
+    <t>PS02-97-03382</t>
   </si>
   <si>
     <t>RMA-12488</t>
   </si>
   <si>
-    <t>PS02-96-21406</t>
+    <t>PS02-96-03235</t>
   </si>
   <si>
     <t>RMA-12489</t>
   </si>
   <si>
-    <t>PS02-97-21504</t>
+    <t>PS02-97-03490</t>
   </si>
   <si>
     <t>RMA-12490</t>
   </si>
   <si>
-    <t>PS02-96-21339</t>
+    <t>PS02-96-03055</t>
   </si>
   <si>
     <t>RMA-12491</t>
   </si>
   <si>
-    <t>PS02-96-21388</t>
+    <t>PS02-96-03186</t>
   </si>
   <si>
     <t>RMA-12492</t>
   </si>
   <si>
-    <t>PS02-95-21267</t>
+    <t>PS02-95-02871</t>
   </si>
   <si>
     <t>RMA-12493</t>
   </si>
   <si>
-    <t>PS02-95-21229</t>
+    <t>PS02-95-02769</t>
   </si>
   <si>
     <t>RMA-12494</t>
   </si>
   <si>
-    <t>PS02-97-21479</t>
+    <t>PS02-97-03429</t>
   </si>
   <si>
     <t>RMA-12495</t>
   </si>
   <si>
-    <t>PS02-96-21383</t>
+    <t>PS02-96-03173</t>
   </si>
   <si>
     <t>RMA-12496</t>
   </si>
   <si>
-    <t>PS02-97-21473</t>
+    <t>PS02-97-03413</t>
   </si>
   <si>
     <t>RMA-12497</t>
   </si>
   <si>
-    <t>PS02-97-21511</t>
+    <t>PS02-97-03509</t>
   </si>
   <si>
     <t>RMA-12524</t>
   </si>
   <si>
-    <t>PS02-08-23952</t>
+    <t>PS02-08-09988</t>
   </si>
   <si>
     <t>473173</t>
@@ -728,7 +728,7 @@
     <t>RMA-12625</t>
   </si>
   <si>
-    <t>PS02-99-21765</t>
+    <t>PS02-99-04184</t>
   </si>
   <si>
     <t>473992</t>
@@ -740,7 +740,7 @@
     <t>RMA-12778</t>
   </si>
   <si>
-    <t>PS02-05-23144</t>
+    <t>PS02-05-07856</t>
   </si>
   <si>
     <t>475093</t>
@@ -752,7 +752,7 @@
     <t>RMA-12783</t>
   </si>
   <si>
-    <t>PS02-99-21784</t>
+    <t>PS02-99-04239</t>
   </si>
   <si>
     <t>475160</t>
@@ -761,7 +761,7 @@
     <t>RMA-12899</t>
   </si>
   <si>
-    <t>PS02-98-21666</t>
+    <t>PS02-98-03922</t>
   </si>
   <si>
     <t>475757</t>
@@ -773,7 +773,7 @@
     <t>RMA-13003</t>
   </si>
   <si>
-    <t>PS02-09-24493</t>
+    <t>PS02-09-11416</t>
   </si>
   <si>
     <t>476584</t>
@@ -785,7 +785,7 @@
     <t>RMA-13106</t>
   </si>
   <si>
-    <t>PS02-11-25155</t>
+    <t>PS02-11-13187</t>
   </si>
   <si>
     <t>477311</t>
@@ -794,7 +794,7 @@
     <t>RMA-13403</t>
   </si>
   <si>
-    <t>PS02-05-23149</t>
+    <t>PS02-05-07869</t>
   </si>
   <si>
     <t>479718</t>
@@ -806,7 +806,7 @@
     <t>RMA-13496</t>
   </si>
   <si>
-    <t>PS02-13-25972</t>
+    <t>PS02-13-15365</t>
   </si>
   <si>
     <t>480430</t>
@@ -815,7 +815,7 @@
     <t>RMA-13528</t>
   </si>
   <si>
-    <t>PS02-01-22254</t>
+    <t>PS02-01-05479</t>
   </si>
   <si>
     <t>480593</t>
@@ -827,7 +827,7 @@
     <t>RMA-13572</t>
   </si>
   <si>
-    <t>PS02-02-22285</t>
+    <t>PS02-02-05555</t>
   </si>
   <si>
     <t>480639</t>
@@ -836,7 +836,7 @@
     <t>RMA-13745</t>
   </si>
   <si>
-    <t>PS02-98-21617</t>
+    <t>PS02-98-03792</t>
   </si>
   <si>
     <t>482126</t>
@@ -848,7 +848,7 @@
     <t>RMA-13775</t>
   </si>
   <si>
-    <t>PS02-03-22699</t>
+    <t>PS02-03-06660</t>
   </si>
   <si>
     <t>482410</t>
@@ -857,7 +857,7 @@
     <t>RMA-13791</t>
   </si>
   <si>
-    <t>PS02-04-23017</t>
+    <t>PS02-04-07512</t>
   </si>
   <si>
     <t>481445</t>
@@ -866,7 +866,7 @@
     <t>RMA-13957</t>
   </si>
   <si>
-    <t>PS02-99-21771</t>
+    <t>PS02-99-04202</t>
   </si>
   <si>
     <t>483672</t>
@@ -875,7 +875,7 @@
     <t>RMA-13974</t>
   </si>
   <si>
-    <t>PS02-98-21660</t>
+    <t>PS02-98-03906</t>
   </si>
   <si>
     <t>483896</t>
@@ -884,7 +884,7 @@
     <t>RMA-14128</t>
   </si>
   <si>
-    <t>PS02-99-21760</t>
+    <t>PS02-99-04173</t>
   </si>
   <si>
     <t>483757</t>
@@ -893,7 +893,7 @@
     <t>RMA-14142</t>
   </si>
   <si>
-    <t>PS02-05-23153</t>
+    <t>PS02-05-07878</t>
   </si>
   <si>
     <t>484835</t>
@@ -902,7 +902,7 @@
     <t>RMA-14234</t>
   </si>
   <si>
-    <t>PS02-10-24643</t>
+    <t>PS02-10-11816</t>
   </si>
   <si>
     <t>485828</t>
@@ -911,7 +911,7 @@
     <t>RMA-14235</t>
   </si>
   <si>
-    <t>PS02-08-24000</t>
+    <t>PS02-08-10118</t>
   </si>
   <si>
     <t>485805</t>
@@ -920,7 +920,7 @@
     <t>RMA-14272</t>
   </si>
   <si>
-    <t>PS02-99-21870</t>
+    <t>PS02-99-04469</t>
   </si>
   <si>
     <t>486171</t>
@@ -929,7 +929,7 @@
     <t>RMA-14321</t>
   </si>
   <si>
-    <t>PS02-99-21754</t>
+    <t>PS02-99-04156</t>
   </si>
   <si>
     <t>486443</t>
@@ -938,7 +938,7 @@
     <t>RMA-14322</t>
   </si>
   <si>
-    <t>PS02-04-22754</t>
+    <t>PS02-04-06810</t>
   </si>
   <si>
     <t>486506</t>
@@ -947,7 +947,7 @@
     <t>RMA-14377</t>
   </si>
   <si>
-    <t>PS02-09-24431</t>
+    <t>PS02-09-11248</t>
   </si>
   <si>
     <t>486896</t>
@@ -956,7 +956,7 @@
     <t>RMA-14391</t>
   </si>
   <si>
-    <t>PS02-00-21924</t>
+    <t>PS02-00-04610</t>
   </si>
   <si>
     <t>486865</t>
@@ -965,7 +965,7 @@
     <t>RMA-14426</t>
   </si>
   <si>
-    <t>PS02-15-26433</t>
+    <t>PS02-15-16604</t>
   </si>
   <si>
     <t>487125</t>
@@ -974,7 +974,7 @@
     <t>RMA-14439</t>
   </si>
   <si>
-    <t>PS02-00-22109</t>
+    <t>PS02-00-05093</t>
   </si>
   <si>
     <t>486743</t>
@@ -983,7 +983,7 @@
     <t>RMA-14466</t>
   </si>
   <si>
-    <t>PS02-98-21665</t>
+    <t>PS02-98-03920</t>
   </si>
   <si>
     <t>487339</t>
@@ -992,7 +992,7 @@
     <t>RMA-14542</t>
   </si>
   <si>
-    <t>PS02-07-23668</t>
+    <t>PS02-07-09228</t>
   </si>
   <si>
     <t>Tarrock Hydro Distribution</t>
@@ -1007,7 +1007,7 @@
     <t>RMA-14545</t>
   </si>
   <si>
-    <t>PS02-01-22135</t>
+    <t>PS02-01-05161</t>
   </si>
   <si>
     <t>488169</t>
@@ -1016,7 +1016,7 @@
     <t>RMA-14570</t>
   </si>
   <si>
-    <t>PS02-10-24564</t>
+    <t>PS02-10-11602</t>
   </si>
   <si>
     <t>488122</t>
@@ -1025,7 +1025,7 @@
     <t>RMA-14618</t>
   </si>
   <si>
-    <t>PS02-12-25427</t>
+    <t>PS02-12-13911</t>
   </si>
   <si>
     <t>488627</t>
@@ -1034,13 +1034,13 @@
     <t>RMA-14735</t>
   </si>
   <si>
-    <t>PS02-02-22270</t>
+    <t>PS02-02-05519</t>
   </si>
   <si>
     <t>RMA-14736</t>
   </si>
   <si>
-    <t>PS02-05-23087</t>
+    <t>PS02-05-07702</t>
   </si>
   <si>
     <t>489206</t>
@@ -1049,7 +1049,7 @@
     <t>RMA-14814</t>
   </si>
   <si>
-    <t>PS02-03-22554</t>
+    <t>PS02-03-06268</t>
   </si>
   <si>
     <t>490068</t>
@@ -1058,7 +1058,7 @@
     <t>RMA-14905</t>
   </si>
   <si>
-    <t>PS02-98-21590</t>
+    <t>PS02-98-03716</t>
   </si>
   <si>
     <t>490567</t>
@@ -1067,7 +1067,7 @@
     <t>RMA-14917</t>
   </si>
   <si>
-    <t>PS02-04-22944</t>
+    <t>PS02-04-07319</t>
   </si>
   <si>
     <t>TARROCK HYDRO DIST</t>
@@ -1079,7 +1079,7 @@
     <t>RMA-15012</t>
   </si>
   <si>
-    <t>PS02-04-22902</t>
+    <t>PS02-04-07203</t>
   </si>
   <si>
     <t>491508</t>
@@ -1088,7 +1088,7 @@
     <t>RMA-15113</t>
   </si>
   <si>
-    <t>PS02-06-23269</t>
+    <t>PS02-06-08181</t>
   </si>
   <si>
     <t>492169</t>
@@ -1097,7 +1097,7 @@
     <t>RMA-15171</t>
   </si>
   <si>
-    <t>PS02-98-21713</t>
+    <t>PS02-98-04043</t>
   </si>
   <si>
     <t>492494</t>
@@ -1106,13 +1106,13 @@
     <t>RMA-15193</t>
   </si>
   <si>
-    <t>PS02-02-22374</t>
+    <t>PS02-02-05786</t>
   </si>
   <si>
     <t>RMA-15215</t>
   </si>
   <si>
-    <t>PS02-98-21631</t>
+    <t>PS02-98-03831</t>
   </si>
   <si>
     <t>492981</t>
@@ -1121,7 +1121,7 @@
     <t>RMA-15289</t>
   </si>
   <si>
-    <t>PS02-99-21853</t>
+    <t>PS02-99-04424</t>
   </si>
   <si>
     <t>492776</t>
@@ -1130,7 +1130,7 @@
     <t>RMA-15394</t>
   </si>
   <si>
-    <t>PS02-03-22434</t>
+    <t>PS02-03-05947</t>
   </si>
   <si>
     <t>494332</t>
@@ -1139,7 +1139,7 @@
     <t>RMA-15416</t>
   </si>
   <si>
-    <t>PS02-11-25240</t>
+    <t>PS02-11-13413</t>
   </si>
   <si>
     <t>494453</t>
@@ -1151,7 +1151,7 @@
     <t>RMA-15456</t>
   </si>
   <si>
-    <t>PS02-15-26559</t>
+    <t>PS02-15-16934</t>
   </si>
   <si>
     <t>494592</t>
@@ -1160,7 +1160,7 @@
     <t>RMA-15501</t>
   </si>
   <si>
-    <t>PS02-03-22562</t>
+    <t>PS02-03-06290</t>
   </si>
   <si>
     <t>493403</t>
@@ -1169,7 +1169,7 @@
     <t>RMA-15604</t>
   </si>
   <si>
-    <t>PS02-07-23815</t>
+    <t>PS02-07-09616</t>
   </si>
   <si>
     <t>495585</t>
@@ -1178,7 +1178,7 @@
     <t>RMA-15669</t>
   </si>
   <si>
-    <t>PS02-00-21985</t>
+    <t>PS02-00-04770</t>
   </si>
   <si>
     <t>496106</t>
@@ -1187,7 +1187,7 @@
     <t>RMA-15861</t>
   </si>
   <si>
-    <t>PS02-10-24863</t>
+    <t>PS02-10-12410</t>
   </si>
   <si>
     <t>497478</t>
@@ -1196,7 +1196,7 @@
     <t>RMA-15878</t>
   </si>
   <si>
-    <t>PS02-03-22489</t>
+    <t>PS02-03-06093</t>
   </si>
   <si>
     <t>WO2104879</t>
@@ -1205,7 +1205,7 @@
     <t>RMA-16008</t>
   </si>
   <si>
-    <t>PS02-07-23541</t>
+    <t>PS02-07-08904</t>
   </si>
   <si>
     <t>WO2109328</t>
@@ -1214,7 +1214,7 @@
     <t>RMA-16117</t>
   </si>
   <si>
-    <t>PS02-04-22734</t>
+    <t>PS02-04-06756</t>
   </si>
   <si>
     <t>WO2113200</t>
@@ -1223,13 +1223,13 @@
     <t>RMA-16125</t>
   </si>
   <si>
-    <t>PS02-08-24038</t>
+    <t>PS02-08-10214</t>
   </si>
   <si>
     <t>RMA-16139</t>
   </si>
   <si>
-    <t>PS02-02-22359</t>
+    <t>PS02-02-05745</t>
   </si>
   <si>
     <t>WO2113997</t>
@@ -1238,118 +1238,118 @@
     <t>RMA-16236</t>
   </si>
   <si>
-    <t>PS02-06-23500</t>
-  </si>
-  <si>
-    <t>WO2117636</t>
+    <t>PS02-06-08793</t>
+  </si>
+  <si>
+    <t>WO2117639</t>
   </si>
   <si>
     <t>RMA-16294</t>
   </si>
   <si>
-    <t>PS02-05-23148</t>
-  </si>
-  <si>
-    <t>WO2119685</t>
+    <t>PS02-05-07868</t>
+  </si>
+  <si>
+    <t>WO2119686</t>
   </si>
   <si>
     <t>RMA-16341</t>
   </si>
   <si>
-    <t>PS02-99-21780</t>
-  </si>
-  <si>
-    <t>WO2121190</t>
+    <t>PS02-99-04228</t>
+  </si>
+  <si>
+    <t>WO2121192</t>
   </si>
   <si>
     <t>RMA-16433</t>
   </si>
   <si>
-    <t>PS02-15-26672</t>
-  </si>
-  <si>
-    <t>WO2124260</t>
+    <t>PS02-15-17237</t>
+  </si>
+  <si>
+    <t>WO2124271</t>
   </si>
   <si>
     <t>RMA-16486</t>
   </si>
   <si>
-    <t>PS02-01-22186</t>
-  </si>
-  <si>
-    <t>WO2126027</t>
+    <t>PS02-01-05295</t>
+  </si>
+  <si>
+    <t>WO2126032</t>
   </si>
   <si>
     <t>RMA-16502</t>
   </si>
   <si>
-    <t>PS02-07-23759</t>
+    <t>PS02-07-09467</t>
   </si>
   <si>
     <t>RMA-16512</t>
   </si>
   <si>
-    <t>PS02-99-21859</t>
-  </si>
-  <si>
-    <t>WO2127035</t>
+    <t>PS02-99-04441</t>
+  </si>
+  <si>
+    <t>WO2127043</t>
   </si>
   <si>
     <t>RMA-16526</t>
   </si>
   <si>
-    <t>PS02-00-21937</t>
-  </si>
-  <si>
-    <t>WO2127560</t>
+    <t>PS02-00-04644</t>
+  </si>
+  <si>
+    <t>WO2127567</t>
   </si>
   <si>
     <t>RMA-16578</t>
   </si>
   <si>
-    <t>PS02-02-22291</t>
-  </si>
-  <si>
-    <t>WO2128905</t>
+    <t>PS02-02-05571</t>
+  </si>
+  <si>
+    <t>WO2128945</t>
   </si>
   <si>
     <t>RMA-16632</t>
   </si>
   <si>
-    <t>PS02-08-24175</t>
-  </si>
-  <si>
-    <t>WO2130443</t>
+    <t>PS02-08-10572</t>
+  </si>
+  <si>
+    <t>WO2130451</t>
   </si>
   <si>
     <t>RMA-16719</t>
   </si>
   <si>
-    <t>PS02-98-21683</t>
+    <t>PS02-98-03968</t>
   </si>
   <si>
     <t>RMA-16848</t>
   </si>
   <si>
-    <t>PS02-06-23287</t>
-  </si>
-  <si>
-    <t>WO2138750</t>
+    <t>PS02-06-08229</t>
+  </si>
+  <si>
+    <t>WO2138780</t>
   </si>
   <si>
     <t>RMA-16849</t>
   </si>
   <si>
-    <t>PS02-02-22283</t>
+    <t>PS02-02-05551</t>
   </si>
   <si>
     <t>RMA-16851</t>
   </si>
   <si>
-    <t>PS02-01-22155</t>
-  </si>
-  <si>
-    <t>WO2138916</t>
+    <t>PS02-01-05213</t>
+  </si>
+  <si>
+    <t>WO2138950</t>
   </si>
   <si>
     <t>NO FAULT FOUND</t>
@@ -1361,79 +1361,79 @@
     <t>RMA-16875</t>
   </si>
   <si>
-    <t>PS02-00-22102</t>
-  </si>
-  <si>
-    <t>WO2139417</t>
+    <t>PS02-00-05074</t>
+  </si>
+  <si>
+    <t>WO2139457</t>
   </si>
   <si>
     <t>RMA-16898</t>
   </si>
   <si>
-    <t>PS02-03-22548</t>
-  </si>
-  <si>
-    <t>WO2141229</t>
+    <t>PS02-03-06250</t>
+  </si>
+  <si>
+    <t>WO2141258</t>
   </si>
   <si>
     <t>RMA-16937</t>
   </si>
   <si>
-    <t>PS02-04-22911</t>
-  </si>
-  <si>
-    <t>WO2141971</t>
+    <t>PS02-04-07227</t>
+  </si>
+  <si>
+    <t>WO2142012</t>
   </si>
   <si>
     <t>RMA-16961</t>
   </si>
   <si>
-    <t>PS02-04-22923</t>
-  </si>
-  <si>
-    <t>WO2143277</t>
+    <t>PS02-04-07261</t>
+  </si>
+  <si>
+    <t>WO2143333</t>
   </si>
   <si>
     <t>RMA-17082</t>
   </si>
   <si>
-    <t>PS02-03-22655</t>
-  </si>
-  <si>
-    <t>WO2147571</t>
+    <t>PS02-03-06544</t>
+  </si>
+  <si>
+    <t>WO2147603</t>
   </si>
   <si>
     <t>RMA-17140</t>
   </si>
   <si>
-    <t>PS02-06-23223</t>
-  </si>
-  <si>
-    <t>WO2149415</t>
+    <t>PS02-06-08058</t>
+  </si>
+  <si>
+    <t>WO2149458</t>
   </si>
   <si>
     <t>RMA-17141</t>
   </si>
   <si>
-    <t>PS02-07-23537</t>
+    <t>PS02-07-08894</t>
   </si>
   <si>
     <t>RMA-17324</t>
   </si>
   <si>
-    <t>PS02-12-25353</t>
-  </si>
-  <si>
-    <t>WO2155870</t>
+    <t>PS02-12-13712</t>
+  </si>
+  <si>
+    <t>WO2155185</t>
   </si>
   <si>
     <t>RMA-17358</t>
   </si>
   <si>
-    <t>PS02-07-23635</t>
-  </si>
-  <si>
-    <t>WO2157422</t>
+    <t>PS02-07-09142</t>
+  </si>
+  <si>
+    <t>WO2157520</t>
   </si>
   <si>
     <t>Electrolytic caps replaced, load tested</t>
@@ -1442,136 +1442,136 @@
     <t>RMA-17359</t>
   </si>
   <si>
-    <t>PS02-14-26193</t>
+    <t>PS02-14-15962</t>
   </si>
   <si>
     <t>RMA-17440</t>
   </si>
   <si>
-    <t>PS02-09-24403</t>
-  </si>
-  <si>
-    <t>WO2161115</t>
+    <t>PS02-09-11173</t>
+  </si>
+  <si>
+    <t>WO2161168</t>
   </si>
   <si>
     <t>RMA-17445</t>
   </si>
   <si>
-    <t>PS02-98-21718</t>
+    <t>PS02-98-04056</t>
   </si>
   <si>
     <t>RMA-17458</t>
   </si>
   <si>
-    <t>PS02-12-25455</t>
-  </si>
-  <si>
-    <t>WO2161444</t>
+    <t>PS02-12-13985</t>
+  </si>
+  <si>
+    <t>WO2161513</t>
   </si>
   <si>
     <t>RMA-17472</t>
   </si>
   <si>
-    <t>PS02-01-22264</t>
-  </si>
-  <si>
-    <t>WO2162149</t>
+    <t>PS02-01-05504</t>
+  </si>
+  <si>
+    <t>WO2162215</t>
   </si>
   <si>
     <t>RMA-17487</t>
   </si>
   <si>
-    <t>PS02-98-21641</t>
-  </si>
-  <si>
-    <t>WO2162536</t>
+    <t>PS02-98-03858</t>
+  </si>
+  <si>
+    <t>WO2162589</t>
   </si>
   <si>
     <t>RMA-17492</t>
   </si>
   <si>
-    <t>PS02-08-23881</t>
-  </si>
-  <si>
-    <t>WO2162742</t>
+    <t>PS02-08-09795</t>
+  </si>
+  <si>
+    <t>WO2162805</t>
   </si>
   <si>
     <t>RMA-17575</t>
   </si>
   <si>
-    <t>PS02-12-25405</t>
-  </si>
-  <si>
-    <t>WO2164823</t>
+    <t>PS02-12-13852</t>
+  </si>
+  <si>
+    <t>WO2164873</t>
   </si>
   <si>
     <t>RMA-17587</t>
   </si>
   <si>
-    <t>PS02-03-22524</t>
-  </si>
-  <si>
-    <t>WO2165886</t>
+    <t>PS02-03-06184</t>
+  </si>
+  <si>
+    <t>WO2165952</t>
   </si>
   <si>
     <t>RMA-17601</t>
   </si>
   <si>
-    <t>PS02-00-22024</t>
-  </si>
-  <si>
-    <t>WO2166229</t>
+    <t>PS02-00-04872</t>
+  </si>
+  <si>
+    <t>WO2166279</t>
   </si>
   <si>
     <t>RMA-17630</t>
   </si>
   <si>
-    <t>PS02-99-21890</t>
-  </si>
-  <si>
-    <t>WO2167323</t>
+    <t>PS02-99-04521</t>
+  </si>
+  <si>
+    <t>WO2167401</t>
   </si>
   <si>
     <t>RMA-17645</t>
   </si>
   <si>
-    <t>PS02-01-22213</t>
-  </si>
-  <si>
-    <t>WO2167591</t>
+    <t>PS02-01-05369</t>
+  </si>
+  <si>
+    <t>WO2167650</t>
   </si>
   <si>
     <t>RMA-17665</t>
   </si>
   <si>
-    <t>PS02-04-23031</t>
-  </si>
-  <si>
-    <t>WO2166642</t>
+    <t>PS02-04-07553</t>
+  </si>
+  <si>
+    <t>WO2166709</t>
   </si>
   <si>
     <t>RMA-17667</t>
   </si>
   <si>
-    <t>PS02-06-23395</t>
+    <t>PS02-06-08508</t>
   </si>
   <si>
     <t>RMA-17686</t>
   </si>
   <si>
-    <t>PS02-06-23250</t>
-  </si>
-  <si>
-    <t>WO2169566</t>
+    <t>PS02-06-08128</t>
+  </si>
+  <si>
+    <t>WO2169620</t>
   </si>
   <si>
     <t>RMA-17734</t>
   </si>
   <si>
-    <t>PS02-11-25064</t>
-  </si>
-  <si>
-    <t>WO2171180</t>
+    <t>PS02-11-12943</t>
+  </si>
+  <si>
+    <t>WO2171233</t>
   </si>
   <si>
     <t>Tested at full load, no fault</t>
@@ -1580,172 +1580,172 @@
     <t>RMA-17736</t>
   </si>
   <si>
-    <t>PS02-98-21594</t>
-  </si>
-  <si>
-    <t>2171128</t>
+    <t>PS02-98-03727</t>
+  </si>
+  <si>
+    <t>2171192</t>
   </si>
   <si>
     <t>RMA-17808</t>
   </si>
   <si>
-    <t>PS02-10-24823</t>
-  </si>
-  <si>
-    <t>WO2173622</t>
+    <t>PS02-10-12300</t>
+  </si>
+  <si>
+    <t>WO2173725</t>
   </si>
   <si>
     <t>RMA-17847</t>
   </si>
   <si>
-    <t>PS02-00-22020</t>
-  </si>
-  <si>
-    <t>WO2175049</t>
+    <t>PS02-00-04861</t>
+  </si>
+  <si>
+    <t>WO2175158</t>
   </si>
   <si>
     <t>RMA-17872</t>
   </si>
   <si>
-    <t>PS02-10-24767</t>
-  </si>
-  <si>
-    <t>WO2175808</t>
+    <t>PS02-10-12146</t>
+  </si>
+  <si>
+    <t>WO2175870</t>
   </si>
   <si>
     <t>RMA-17908</t>
   </si>
   <si>
-    <t>PS02-10-24670</t>
-  </si>
-  <si>
-    <t>WO2176629</t>
+    <t>PS02-10-11889</t>
+  </si>
+  <si>
+    <t>WO2176704</t>
   </si>
   <si>
     <t>RMA-17913</t>
   </si>
   <si>
-    <t>PS02-00-22085</t>
-  </si>
-  <si>
-    <t>WO2176727</t>
+    <t>PS02-00-05031</t>
+  </si>
+  <si>
+    <t>WO2176779</t>
   </si>
   <si>
     <t>RMA-17976</t>
   </si>
   <si>
-    <t>PS02-11-24879</t>
-  </si>
-  <si>
-    <t>WO2179125</t>
+    <t>PS02-11-12454</t>
+  </si>
+  <si>
+    <t>WO2179204</t>
   </si>
   <si>
     <t>RMA-18031</t>
   </si>
   <si>
-    <t>PS02-12-25608</t>
-  </si>
-  <si>
-    <t>WO2180801</t>
+    <t>PS02-12-14389</t>
+  </si>
+  <si>
+    <t>WO2180879</t>
   </si>
   <si>
     <t>RMA-18032</t>
   </si>
   <si>
-    <t>PS02-04-22879</t>
+    <t>PS02-04-07143</t>
   </si>
   <si>
     <t>RMA-18036</t>
   </si>
   <si>
-    <t>PS02-99-21759</t>
+    <t>PS02-99-04171</t>
   </si>
   <si>
     <t>RMA-18077</t>
   </si>
   <si>
-    <t>PS02-10-24596</t>
-  </si>
-  <si>
-    <t>WO2182237</t>
+    <t>PS02-10-11689</t>
+  </si>
+  <si>
+    <t>WO2182327</t>
   </si>
   <si>
     <t>RMA-18160</t>
   </si>
   <si>
-    <t>PS02-07-23754</t>
-  </si>
-  <si>
-    <t>WO2185380</t>
+    <t>PS02-07-09454</t>
+  </si>
+  <si>
+    <t>WO2185458</t>
   </si>
   <si>
     <t>RMA-18220</t>
   </si>
   <si>
-    <t>PS02-98-21624</t>
-  </si>
-  <si>
-    <t>WO2187510</t>
+    <t>PS02-98-03811</t>
+  </si>
+  <si>
+    <t>WO2187594</t>
   </si>
   <si>
     <t>RMA-18279</t>
   </si>
   <si>
-    <t>PS02-03-22578</t>
-  </si>
-  <si>
-    <t>WO2189762</t>
+    <t>PS02-03-06334</t>
+  </si>
+  <si>
+    <t>WO2189837</t>
   </si>
   <si>
     <t>RMA-18285</t>
   </si>
   <si>
-    <t>PS02-04-23036</t>
-  </si>
-  <si>
-    <t>WO2189817</t>
+    <t>PS02-04-07566</t>
+  </si>
+  <si>
+    <t>WO2189900</t>
   </si>
   <si>
     <t>RMA-18310</t>
   </si>
   <si>
-    <t>PS02-02-22295</t>
-  </si>
-  <si>
-    <t>WO2191566</t>
+    <t>PS02-02-05582</t>
+  </si>
+  <si>
+    <t>WO2191651</t>
   </si>
   <si>
     <t>RMA-18351</t>
   </si>
   <si>
-    <t>PS02-03-22445</t>
-  </si>
-  <si>
-    <t>WO2192610</t>
+    <t>PS02-03-05978</t>
+  </si>
+  <si>
+    <t>WO2192986</t>
   </si>
   <si>
     <t>RMA-18354</t>
   </si>
   <si>
-    <t>PS02-09-24297</t>
+    <t>PS02-09-10897</t>
   </si>
   <si>
     <t>RMA-18374</t>
   </si>
   <si>
-    <t>PS02-06-23228</t>
-  </si>
-  <si>
-    <t>WO2193743</t>
+    <t>PS02-06-08070</t>
+  </si>
+  <si>
+    <t>WO2193863</t>
   </si>
   <si>
     <t>RMA-18422</t>
   </si>
   <si>
-    <t>PS02-99-21838</t>
-  </si>
-  <si>
-    <t>WO2195333</t>
+    <t>PS02-99-04385</t>
+  </si>
+  <si>
+    <t>WO2195418</t>
   </si>
   <si>
     <t>NFF on bench, 24 h burn-in OK</t>
@@ -1754,52 +1754,52 @@
     <t>RMA-18429</t>
   </si>
   <si>
-    <t>PS02-03-22449</t>
-  </si>
-  <si>
-    <t>WO2195550</t>
+    <t>PS02-03-05986</t>
+  </si>
+  <si>
+    <t>WO2195660</t>
   </si>
   <si>
     <t>RMA-18430</t>
   </si>
   <si>
-    <t>PS02-00-22122</t>
-  </si>
-  <si>
-    <t>WO2195493</t>
+    <t>PS02-00-05126</t>
+  </si>
+  <si>
+    <t>WO2195601</t>
   </si>
   <si>
     <t>RMA-18433</t>
   </si>
   <si>
-    <t>PS02-02-22397</t>
-  </si>
-  <si>
-    <t>WO2195618</t>
+    <t>PS02-02-05846</t>
+  </si>
+  <si>
+    <t>WO2195734</t>
   </si>
   <si>
     <t>RMA-18472</t>
   </si>
   <si>
-    <t>PS02-03-22458</t>
-  </si>
-  <si>
-    <t>WO2197047</t>
+    <t>PS02-03-06009</t>
+  </si>
+  <si>
+    <t>WO2197181</t>
   </si>
   <si>
     <t>RMA-18476</t>
   </si>
   <si>
-    <t>PS02-09-24507</t>
-  </si>
-  <si>
-    <t>WO2197373</t>
+    <t>PS02-09-11454</t>
+  </si>
+  <si>
+    <t>WO2197636</t>
   </si>
   <si>
     <t>RMA-18493</t>
   </si>
   <si>
-    <t>WO2197968</t>
+    <t>WO2198036</t>
   </si>
   <si>
     <t>Warranty, ref RMA-18279. Input fuse open, fuse and bulk caps replaced</t>
@@ -1808,310 +1808,310 @@
     <t>RMA-18511</t>
   </si>
   <si>
-    <t>PS02-99-21888</t>
-  </si>
-  <si>
-    <t>WO2198563</t>
+    <t>PS02-99-04517</t>
+  </si>
+  <si>
+    <t>WO2198649</t>
   </si>
   <si>
     <t>RMA-18585</t>
   </si>
   <si>
-    <t>PS02-15-26866</t>
-  </si>
-  <si>
-    <t>WO2201066</t>
+    <t>PS02-15-17749</t>
+  </si>
+  <si>
+    <t>WO2201160</t>
   </si>
   <si>
     <t>RMA-18610</t>
   </si>
   <si>
-    <t>PS02-15-26462</t>
-  </si>
-  <si>
-    <t>WO2201935</t>
+    <t>PS02-15-16679</t>
+  </si>
+  <si>
+    <t>WO2202281</t>
   </si>
   <si>
     <t>RMA-18683</t>
   </si>
   <si>
-    <t>PS02-01-22174</t>
-  </si>
-  <si>
-    <t>WO2204738</t>
+    <t>PS02-01-05264</t>
+  </si>
+  <si>
+    <t>WO2204859</t>
   </si>
   <si>
     <t>RMA-18684</t>
   </si>
   <si>
-    <t>PS02-99-21896</t>
+    <t>PS02-99-04537</t>
   </si>
   <si>
     <t>RMA-18687</t>
   </si>
   <si>
-    <t>PS02-02-22305</t>
-  </si>
-  <si>
-    <t>WO2204987</t>
+    <t>PS02-02-05605</t>
+  </si>
+  <si>
+    <t>WO2205299</t>
   </si>
   <si>
     <t>RMA-18748</t>
   </si>
   <si>
-    <t>PS02-03-22718</t>
-  </si>
-  <si>
-    <t>WO2207160</t>
+    <t>PS02-03-06712</t>
+  </si>
+  <si>
+    <t>WO2207277</t>
   </si>
   <si>
     <t>RMA-18749</t>
   </si>
   <si>
-    <t>PS02-04-23047</t>
-  </si>
-  <si>
-    <t>WO2207261</t>
+    <t>PS02-04-07594</t>
+  </si>
+  <si>
+    <t>WO2207397</t>
   </si>
   <si>
     <t>RMA-18779</t>
   </si>
   <si>
-    <t>PS02-99-21805</t>
-  </si>
-  <si>
-    <t>WO2207933</t>
+    <t>PS02-99-04295</t>
+  </si>
+  <si>
+    <t>WO2208053</t>
   </si>
   <si>
     <t>RMA-18780</t>
   </si>
   <si>
-    <t>PS02-98-21605</t>
-  </si>
-  <si>
-    <t>WO2207997</t>
+    <t>PS02-98-03757</t>
+  </si>
+  <si>
+    <t>WO2208120</t>
   </si>
   <si>
     <t>RMA-18872</t>
   </si>
   <si>
-    <t>PS02-10-24679</t>
-  </si>
-  <si>
-    <t>2211017</t>
+    <t>PS02-10-11911</t>
+  </si>
+  <si>
+    <t>2211149</t>
   </si>
   <si>
     <t>RMA-18910</t>
   </si>
   <si>
-    <t>PS02-08-23900</t>
-  </si>
-  <si>
-    <t>WO2212606</t>
+    <t>PS02-08-09847</t>
+  </si>
+  <si>
+    <t>WO2212761</t>
   </si>
   <si>
     <t>RMA-18968</t>
   </si>
   <si>
-    <t>PS02-04-22795</t>
-  </si>
-  <si>
-    <t>WO2214579</t>
+    <t>PS02-04-06919</t>
+  </si>
+  <si>
+    <t>WO2214729</t>
   </si>
   <si>
     <t>RMA-19026</t>
   </si>
   <si>
-    <t>PS02-06-23380</t>
-  </si>
-  <si>
-    <t>WO2216395</t>
+    <t>PS02-06-08468</t>
+  </si>
+  <si>
+    <t>WO2216528</t>
   </si>
   <si>
     <t>RMA-19036</t>
   </si>
   <si>
-    <t>PS02-02-22373</t>
-  </si>
-  <si>
-    <t>WO2216822</t>
+    <t>PS02-02-05783</t>
+  </si>
+  <si>
+    <t>WO2216972</t>
   </si>
   <si>
     <t>RMA-19070</t>
   </si>
   <si>
-    <t>PS02-08-24222</t>
-  </si>
-  <si>
-    <t>WO2217914</t>
+    <t>PS02-08-10701</t>
+  </si>
+  <si>
+    <t>WO2218283</t>
   </si>
   <si>
     <t>RMA-19073</t>
   </si>
   <si>
-    <t>PS02-04-22973</t>
-  </si>
-  <si>
-    <t>WO2218330</t>
+    <t>PS02-04-07396</t>
+  </si>
+  <si>
+    <t>WO2218464</t>
   </si>
   <si>
     <t>RMA-19093</t>
   </si>
   <si>
-    <t>PS02-13-25993</t>
-  </si>
-  <si>
-    <t>WO2218984</t>
+    <t>PS02-13-15423</t>
+  </si>
+  <si>
+    <t>WO2219132</t>
   </si>
   <si>
     <t>RMA-19138</t>
   </si>
   <si>
-    <t>PS02-06-23453</t>
-  </si>
-  <si>
-    <t>WO2220454</t>
+    <t>PS02-06-08669</t>
+  </si>
+  <si>
+    <t>WO2220617</t>
   </si>
   <si>
     <t>RMA-19238</t>
   </si>
   <si>
-    <t>PS02-03-22476</t>
-  </si>
-  <si>
-    <t>WO2223672</t>
+    <t>PS02-03-06059</t>
+  </si>
+  <si>
+    <t>WO2223807</t>
   </si>
   <si>
     <t>RMA-19260</t>
   </si>
   <si>
-    <t>PS02-07-23508</t>
-  </si>
-  <si>
-    <t>WO2224442</t>
+    <t>PS02-07-08814</t>
+  </si>
+  <si>
+    <t>WO2224557</t>
   </si>
   <si>
     <t>RMA-19261</t>
   </si>
   <si>
-    <t>PS02-03-22424</t>
+    <t>PS02-03-05919</t>
   </si>
   <si>
     <t>RMA-19284</t>
   </si>
   <si>
-    <t>PS02-01-22152</t>
-  </si>
-  <si>
-    <t>WO2225396</t>
+    <t>PS02-01-05204</t>
+  </si>
+  <si>
+    <t>WO2225572</t>
   </si>
   <si>
     <t>RMA-19285</t>
   </si>
   <si>
-    <t>PS02-15-26806</t>
-  </si>
-  <si>
-    <t>WO 2225396</t>
+    <t>PS02-15-17591</t>
+  </si>
+  <si>
+    <t>WO 2225572</t>
   </si>
   <si>
     <t>RMA-19307</t>
   </si>
   <si>
-    <t>PS02-09-24478</t>
-  </si>
-  <si>
-    <t>WO2226101</t>
+    <t>PS02-09-11375</t>
+  </si>
+  <si>
+    <t>WO2226268</t>
   </si>
   <si>
     <t>RMA-19308</t>
   </si>
   <si>
-    <t>PS02-05-23090</t>
+    <t>PS02-05-07710</t>
   </si>
   <si>
     <t>RMA-19310</t>
   </si>
   <si>
-    <t>PS02-99-21846</t>
-  </si>
-  <si>
-    <t>WO2225844</t>
+    <t>PS02-99-04406</t>
+  </si>
+  <si>
+    <t>WO2226029</t>
   </si>
   <si>
     <t>RMA-19311</t>
   </si>
   <si>
-    <t>PS02-05-23208</t>
-  </si>
-  <si>
-    <t>WO2225984</t>
+    <t>PS02-05-08024</t>
+  </si>
+  <si>
+    <t>WO2226142</t>
   </si>
   <si>
     <t>RMA-19366</t>
   </si>
   <si>
-    <t>PS02-15-26814</t>
-  </si>
-  <si>
-    <t>WO2228408</t>
+    <t>PS02-15-17613</t>
+  </si>
+  <si>
+    <t>WO2228560</t>
   </si>
   <si>
     <t>RMA-19373</t>
   </si>
   <si>
-    <t>PS02-03-22408</t>
-  </si>
-  <si>
-    <t>WO2228523</t>
+    <t>PS02-03-05875</t>
+  </si>
+  <si>
+    <t>WO2228689</t>
   </si>
   <si>
     <t>RMA-19413</t>
   </si>
   <si>
-    <t>PS02-04-22853</t>
-  </si>
-  <si>
-    <t>WO2229857</t>
+    <t>PS02-04-07075</t>
+  </si>
+  <si>
+    <t>WO2230052</t>
   </si>
   <si>
     <t>RMA-19455</t>
   </si>
   <si>
-    <t>PS02-01-22214</t>
-  </si>
-  <si>
-    <t>WO2230927</t>
+    <t>PS02-01-05372</t>
+  </si>
+  <si>
+    <t>WO2231115</t>
   </si>
   <si>
     <t>RMA-19460</t>
   </si>
   <si>
-    <t>PS02-03-22689</t>
-  </si>
-  <si>
-    <t>WO2231364</t>
+    <t>PS02-03-06634</t>
+  </si>
+  <si>
+    <t>WO2231540</t>
   </si>
   <si>
     <t>RMA-19466</t>
   </si>
   <si>
-    <t>PS02-10-24751</t>
+    <t>PS02-10-12105</t>
   </si>
   <si>
     <t>RMA-19491</t>
   </si>
   <si>
-    <t>PS02-06-23317</t>
-  </si>
-  <si>
-    <t>WO2232324</t>
+    <t>PS02-06-08305</t>
+  </si>
+  <si>
+    <t>WO2232465</t>
   </si>
   <si>
     <t>RMA-19527</t>
   </si>
   <si>
-    <t>WO2233277</t>
+    <t>WO2233455</t>
   </si>
   <si>
     <t>Warranty, ref RMA-19036</t>
@@ -2120,10 +2120,10 @@
     <t>RMA-19607</t>
   </si>
   <si>
-    <t>PS02-18-27430</t>
-  </si>
-  <si>
-    <t>WO2235975</t>
+    <t>PS02-18-19247</t>
+  </si>
+  <si>
+    <t>WO2236115</t>
   </si>
   <si>
     <t>OPEN</t>
@@ -2132,37 +2132,37 @@
     <t>RMA-19608</t>
   </si>
   <si>
-    <t>PS02-05-23132</t>
-  </si>
-  <si>
-    <t>WO2236082</t>
+    <t>PS02-05-07821</t>
+  </si>
+  <si>
+    <t>WO2236269</t>
   </si>
   <si>
     <t>RMA-19628</t>
   </si>
   <si>
-    <t>PS02-02-22320</t>
-  </si>
-  <si>
-    <t>WO2236998</t>
+    <t>PS02-02-05646</t>
+  </si>
+  <si>
+    <t>WO2237428</t>
   </si>
   <si>
     <t>RMA-19662</t>
   </si>
   <si>
-    <t>PS02-99-21775</t>
-  </si>
-  <si>
-    <t>WO2238475</t>
+    <t>PS02-99-04213</t>
+  </si>
+  <si>
+    <t>WO2238818</t>
   </si>
   <si>
     <t>RMA-19696</t>
   </si>
   <si>
-    <t>PS02-05-23113</t>
-  </si>
-  <si>
-    <t>WO2239624</t>
+    <t>PS02-05-07772</t>
+  </si>
+  <si>
+    <t>WO2239848</t>
   </si>
   <si>
     <t>Awaiting caps</t>
@@ -2171,10 +2171,10 @@
     <t>RMA-19704</t>
   </si>
   <si>
-    <t>PS02-13-25936</t>
-  </si>
-  <si>
-    <t>WO2239671</t>
+    <t>PS02-13-15266</t>
+  </si>
+  <si>
+    <t>WO2239881</t>
   </si>
 </sst>
 </file>
